--- a/lat_claude.xlsx
+++ b/lat_claude.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DB90231EFD63CB83B761751BB74D2411A4BD069F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC4004D-C00F-4B66-A6D2-DE18279A2898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1110" windowWidth="11400" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POSICIONES" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="132">
   <si>
     <t>fecha</t>
   </si>
@@ -418,6 +418,9 @@
   </si>
   <si>
     <t>Esperando para descargar tropas</t>
+  </si>
+  <si>
+    <t>07/12/1786</t>
   </si>
 </sst>
 </file>
@@ -440,33 +443,39 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2188,8 +2197,8 @@
       <c r="L53" s="7"/>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8">
-        <v>43076</v>
+      <c r="A54" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>85</v>

--- a/lat_claude.xlsx
+++ b/lat_claude.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC4004D-C00F-4B66-A6D2-DE18279A2898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="1950" yWindow="1110" windowWidth="11400" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="POSICIONES" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="POSICIONES" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="kcOFg+kGFRKbLW+uIxLaGXeLJt4gzB//gIk76z592ME="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YUqHA3DHMydyRE56dyeACfOdA3kyMUg9AI+rpOrThlw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="158">
   <si>
     <t>fecha</t>
   </si>
@@ -252,6 +243,84 @@
     <t>En combate</t>
   </si>
   <si>
+    <t>14/4/1784</t>
+  </si>
+  <si>
+    <t>ESC0006</t>
+  </si>
+  <si>
+    <t>RUT0028</t>
+  </si>
+  <si>
+    <t>Destino Cádiz, escuadra convoy con caudales</t>
+  </si>
+  <si>
+    <t>12/05/1784</t>
+  </si>
+  <si>
+    <t>BUQ00047</t>
+  </si>
+  <si>
+    <t>RUT0029</t>
+  </si>
+  <si>
+    <t>Avería, rompe formación y regresa a Callao</t>
+  </si>
+  <si>
+    <t>13/6/1784</t>
+  </si>
+  <si>
+    <t>Reparaciones de emergencia y descarga parcial de cargamento</t>
+  </si>
+  <si>
+    <t>4/8/1784</t>
+  </si>
+  <si>
+    <t>01/09/1784</t>
+  </si>
+  <si>
+    <t>Destino Callao</t>
+  </si>
+  <si>
+    <t>partida</t>
+  </si>
+  <si>
+    <t>15/09/1784</t>
+  </si>
+  <si>
+    <t>arribada</t>
+  </si>
+  <si>
+    <t>21/2/1785</t>
+  </si>
+  <si>
+    <t>22/2/1785</t>
+  </si>
+  <si>
+    <t>BUQ00046</t>
+  </si>
+  <si>
+    <t>Descargando cargamento</t>
+  </si>
+  <si>
+    <t>25/2/1785</t>
+  </si>
+  <si>
+    <t>INF017</t>
+  </si>
+  <si>
+    <t>inactivo</t>
+  </si>
+  <si>
+    <t>desarmado</t>
+  </si>
+  <si>
+    <t>27/7/1784</t>
+  </si>
+  <si>
+    <t>BUQ00023</t>
+  </si>
+  <si>
     <t>15/12/1785</t>
   </si>
   <si>
@@ -267,21 +336,36 @@
     <t>04/01/1786</t>
   </si>
   <si>
-    <t>arribada</t>
-  </si>
-  <si>
     <t>05/01/1786</t>
   </si>
   <si>
     <t>06/01/1786</t>
   </si>
   <si>
+    <t>17/3/1786</t>
+  </si>
+  <si>
+    <t>BUQ00091</t>
+  </si>
+  <si>
+    <t>RUT0026</t>
+  </si>
+  <si>
+    <t>Destino Cádiz de regreso de expedición científica</t>
+  </si>
+  <si>
+    <t>18/3/1786</t>
+  </si>
+  <si>
     <t>24/04/1786</t>
   </si>
   <si>
     <t>Esperando órdenes del Virrey</t>
   </si>
   <si>
+    <t>7/12/1786</t>
+  </si>
+  <si>
     <t>BUQ00034</t>
   </si>
   <si>
@@ -363,9 +447,6 @@
     <t>2/11/1787</t>
   </si>
   <si>
-    <t>Descargando cargamento</t>
-  </si>
-  <si>
     <t>3/11/1787</t>
   </si>
   <si>
@@ -387,15 +468,6 @@
     <t>25/09/1787</t>
   </si>
   <si>
-    <t>INF017</t>
-  </si>
-  <si>
-    <t>inactivo</t>
-  </si>
-  <si>
-    <t>desarmado</t>
-  </si>
-  <si>
     <t>15/02/1788</t>
   </si>
   <si>
@@ -418,64 +490,59 @@
   </si>
   <si>
     <t>Esperando para descargar tropas</t>
-  </si>
-  <si>
-    <t>07/12/1786</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -483,17 +550,11 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -507,57 +568,82 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="22">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -747,25 +833,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1018"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col customWidth="1" min="4" max="4" width="11.13"/>
+    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="6" max="6" width="15.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,7 +887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -817,7 +901,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5">
-        <v>-20.533300000000001</v>
+        <v>-20.5333</v>
       </c>
       <c r="H2" s="5">
         <v>-30.5167</v>
@@ -835,7 +919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -849,7 +933,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
-        <v>-20.533300000000001</v>
+        <v>-20.5333</v>
       </c>
       <c r="H3" s="5">
         <v>-30.5167</v>
@@ -867,7 +951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -879,10 +963,10 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5">
-        <v>36.433329999999998</v>
+        <v>36.43333</v>
       </c>
       <c r="H4" s="5">
-        <v>-6.6283399999999997</v>
+        <v>-6.62834</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -895,7 +979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -907,10 +991,10 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
-        <v>35.634720000000002</v>
+        <v>35.63472</v>
       </c>
       <c r="H5" s="5">
-        <v>-7.6377899999999999</v>
+        <v>-7.63779</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>15</v>
@@ -925,7 +1009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -940,7 +1024,7 @@
         <v>34.36833</v>
       </c>
       <c r="H6" s="5">
-        <v>-8.9044600000000003</v>
+        <v>-8.90446</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>15</v>
@@ -955,7 +1039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -967,10 +1051,10 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5">
-        <v>33.533329999999999</v>
+        <v>33.53333</v>
       </c>
       <c r="H7" s="5">
-        <v>-9.9711200000000009</v>
+        <v>-9.97112</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>15</v>
@@ -985,7 +1069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -997,7 +1081,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5">
-        <v>32.608330000000002</v>
+        <v>32.60833</v>
       </c>
       <c r="H8" s="5">
         <v>-10.96279</v>
@@ -1015,7 +1099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
@@ -1029,7 +1113,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
-        <v>36.383330000000001</v>
+        <v>36.38333</v>
       </c>
       <c r="H9" s="5">
         <v>-6.65557</v>
@@ -1045,7 +1129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
@@ -1059,10 +1143,10 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5">
-        <v>35.733330000000002</v>
+        <v>35.73333</v>
       </c>
       <c r="H10" s="5">
-        <v>-7.5388999999999999</v>
+        <v>-7.5389</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>15</v>
@@ -1077,7 +1161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
@@ -1091,10 +1175,10 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5">
-        <v>34.866669999999999</v>
+        <v>34.86667</v>
       </c>
       <c r="H11" s="5">
-        <v>-8.7055699999999998</v>
+        <v>-8.70557</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>15</v>
@@ -1109,7 +1193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>35</v>
       </c>
@@ -1123,10 +1207,10 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5">
-        <v>34.033329999999999</v>
+        <v>34.03333</v>
       </c>
       <c r="H12" s="5">
-        <v>-9.8555700000000002</v>
+        <v>-9.85557</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>15</v>
@@ -1141,7 +1225,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1155,10 +1239,10 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5">
-        <v>33.633330000000001</v>
+        <v>33.63333</v>
       </c>
       <c r="H13" s="5">
-        <v>-10.172230000000001</v>
+        <v>-10.17223</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>15</v>
@@ -1173,7 +1257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -1190,7 +1274,7 @@
         <v>32.9</v>
       </c>
       <c r="H14" s="5">
-        <v>-10.655570000000001</v>
+        <v>-10.65557</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>15</v>
@@ -1205,7 +1289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
@@ -1219,10 +1303,10 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
-        <v>32.483330000000002</v>
+        <v>32.48333</v>
       </c>
       <c r="H15" s="5">
-        <v>-10.922230000000001</v>
+        <v>-10.92223</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>15</v>
@@ -1237,7 +1321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
@@ -1251,10 +1335,10 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5">
-        <v>32.183329999999998</v>
+        <v>32.18333</v>
       </c>
       <c r="H16" s="5">
-        <v>-12.572229999999999</v>
+        <v>-12.57223</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>15</v>
@@ -1269,7 +1353,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1283,7 +1367,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5">
-        <v>30.833300000000001</v>
+        <v>30.8333</v>
       </c>
       <c r="H17" s="5">
         <v>-14.22223</v>
@@ -1301,7 +1385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
@@ -1318,7 +1402,7 @@
         <v>29.25</v>
       </c>
       <c r="H18" s="5">
-        <v>-16.005569999999999</v>
+        <v>-16.00557</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>15</v>
@@ -1333,7 +1417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
@@ -1350,7 +1434,7 @@
         <v>27.5</v>
       </c>
       <c r="H19" s="5">
-        <v>-17.288900000000002</v>
+        <v>-17.2889</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>15</v>
@@ -1365,7 +1449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -1382,7 +1466,7 @@
         <v>-12.0611</v>
       </c>
       <c r="H20" s="5">
-        <v>-77.146900000000002</v>
+        <v>-77.1469</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>15</v>
@@ -1394,7 +1478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>46</v>
       </c>
@@ -1426,7 +1510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>48</v>
       </c>
@@ -1443,7 +1527,7 @@
         <v>-13.3</v>
       </c>
       <c r="H22" s="4">
-        <v>-81.133369999999999</v>
+        <v>-81.13337</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>15</v>
@@ -1458,7 +1542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>49</v>
       </c>
@@ -1475,7 +1559,7 @@
         <v>-13.85</v>
       </c>
       <c r="H23" s="4">
-        <v>-81.866699999999994</v>
+        <v>-81.8667</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>15</v>
@@ -1490,7 +1574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>50</v>
       </c>
@@ -1504,7 +1588,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <v>-15.216659999999999</v>
+        <v>-15.21666</v>
       </c>
       <c r="H24" s="4">
         <v>-83.45</v>
@@ -1522,7 +1606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>51</v>
       </c>
@@ -1536,10 +1620,10 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
-        <v>-16.399999999999999</v>
+        <v>-16.4</v>
       </c>
       <c r="H25" s="4">
-        <v>-84.833299999999994</v>
+        <v>-84.8333</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>15</v>
@@ -1554,7 +1638,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>52</v>
       </c>
@@ -1568,7 +1652,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
-        <v>-17.533300000000001</v>
+        <v>-17.5333</v>
       </c>
       <c r="H26" s="4">
         <v>-86.5167</v>
@@ -1586,7 +1670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
@@ -1600,7 +1684,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <v>-18.133299999999998</v>
+        <v>-18.1333</v>
       </c>
       <c r="H27" s="4">
         <v>-87.55</v>
@@ -1618,7 +1702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
@@ -1635,7 +1719,7 @@
         <v>-20.5167</v>
       </c>
       <c r="H28" s="4">
-        <v>-88.466700000000003</v>
+        <v>-88.4667</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>15</v>
@@ -1650,7 +1734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>55</v>
       </c>
@@ -1674,7 +1758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>56</v>
       </c>
@@ -1698,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>57</v>
       </c>
@@ -1712,10 +1796,10 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4">
-        <v>-25.616700000000002</v>
+        <v>-25.6167</v>
       </c>
       <c r="H31" s="4">
-        <v>-89.566699999999997</v>
+        <v>-89.5667</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>15</v>
@@ -1730,7 +1814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>58</v>
       </c>
@@ -1740,7 +1824,7 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4">
-        <v>36.529800000000002</v>
+        <v>36.5298</v>
       </c>
       <c r="H32" s="4">
         <v>-6.2923</v>
@@ -1755,7 +1839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
@@ -1767,10 +1851,10 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4">
-        <v>36.416670000000003</v>
+        <v>36.41667</v>
       </c>
       <c r="H33" s="4">
-        <v>-6.6055700000000002</v>
+        <v>-6.60557</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>15</v>
@@ -1785,7 +1869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>63</v>
       </c>
@@ -1797,10 +1881,10 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4">
-        <v>35.916670000000003</v>
+        <v>35.91667</v>
       </c>
       <c r="H34" s="4">
-        <v>-7.4389000000000003</v>
+        <v>-7.4389</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>15</v>
@@ -1815,7 +1899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>64</v>
       </c>
@@ -1827,10 +1911,10 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4">
-        <v>36.674999999999997</v>
+        <v>36.675</v>
       </c>
       <c r="H35" s="4">
-        <v>-7.0805699999999998</v>
+        <v>-7.08057</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>15</v>
@@ -1845,7 +1929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>65</v>
       </c>
@@ -1857,10 +1941,10 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4">
-        <v>36.666670000000003</v>
+        <v>36.66667</v>
       </c>
       <c r="H36" s="4">
-        <v>-7.5388999999999999</v>
+        <v>-7.5389</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>15</v>
@@ -1875,7 +1959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>66</v>
       </c>
@@ -1887,10 +1971,10 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4">
-        <v>36.608330000000002</v>
+        <v>36.60833</v>
       </c>
       <c r="H37" s="4">
-        <v>-8.1555800000000005</v>
+        <v>-8.15558</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>15</v>
@@ -1905,7 +1989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>67</v>
       </c>
@@ -1917,10 +2001,10 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4">
-        <v>36.866669999999999</v>
+        <v>36.86667</v>
       </c>
       <c r="H38" s="4">
-        <v>-9.0889000000000006</v>
+        <v>-9.0889</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>15</v>
@@ -1935,7 +2019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>68</v>
       </c>
@@ -1945,7 +2029,7 @@
       </c>
       <c r="D39" s="4"/>
       <c r="G39" s="4">
-        <v>36.616669999999999</v>
+        <v>36.61667</v>
       </c>
       <c r="H39" s="4">
         <v>-10.59723</v>
@@ -1963,7 +2047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>69</v>
       </c>
@@ -1973,10 +2057,10 @@
       </c>
       <c r="D40" s="4"/>
       <c r="G40" s="4">
-        <v>36.516669999999998</v>
+        <v>36.51667</v>
       </c>
       <c r="H40" s="4">
-        <v>-11.572229999999999</v>
+        <v>-11.57223</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>15</v>
@@ -1991,27 +2075,27 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -2024,10 +2108,10 @@
         <v>73</v>
       </c>
       <c r="G45" s="4">
-        <v>36.818055999999999</v>
+        <v>36.818056</v>
       </c>
       <c r="H45" s="4">
-        <v>-8.5636109999999999</v>
+        <v>-8.563611</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>15</v>
@@ -2042,81 +2126,98 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>44</v>
-      </c>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
       <c r="K46" s="4"/>
-      <c r="L46" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="L46" s="4"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="7" t="s">
         <v>77</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4" t="s">
+      <c r="F47" s="4"/>
+      <c r="G47" s="8">
+        <v>-12.0611</v>
+      </c>
+      <c r="H47" s="8">
+        <v>-77.1469</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" s="7" t="s">
         <v>78</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="E48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4" t="s">
-        <v>78</v>
+      <c r="F48" s="4"/>
+      <c r="G48" s="10">
+        <v>-42.61667</v>
+      </c>
+      <c r="H48" s="10">
+        <v>-76.1923</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G49" s="6">
-        <v>19.1738</v>
-      </c>
-      <c r="H49" s="6">
-        <v>-96.134200000000007</v>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="8">
+        <v>-36.7382</v>
+      </c>
+      <c r="H49" s="8">
+        <v>-73.1388</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>15</v>
@@ -2124,53 +2225,74 @@
       <c r="J49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L49" s="7" t="s">
+      <c r="K49" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="8">
+        <v>-22.881353</v>
+      </c>
+      <c r="H50" s="8">
+        <v>-43.182717</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="12"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="C52" s="7"/>
+      <c r="D52" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G50" s="6">
-        <v>19.1738</v>
-      </c>
-      <c r="H50" s="6">
-        <v>-96.134200000000007</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52" s="6">
-        <v>19.1738</v>
-      </c>
-      <c r="H52" s="6">
-        <v>-96.134200000000007</v>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="8">
+        <v>-36.7382</v>
+      </c>
+      <c r="H52" s="8">
+        <v>-73.1388</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>15</v>
@@ -2179,115 +2301,96 @@
         <v>16</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8"/>
-      <c r="B53" s="7"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-    </row>
-    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54" s="9">
-        <v>43.479100000000003</v>
-      </c>
-      <c r="H54" s="9">
-        <v>-8.2375000000000007</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="7"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="9">
-        <v>43.475999999999999</v>
-      </c>
-      <c r="H56" s="9">
-        <v>-8.2859999999999996</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K56" s="7" t="s">
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L56" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="8"/>
+      <c r="B53" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" s="8">
+        <v>-12.0611</v>
+      </c>
+      <c r="H53" s="8">
+        <v>-77.1469</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="B57" s="7"/>
+      <c r="C57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
+      <c r="G57" s="13">
+        <v>36.5298</v>
+      </c>
+      <c r="H57" s="13">
+        <v>-6.2923</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="11" t="s">
         <v>90</v>
       </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="B58" s="7" t="s">
-        <v>85</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="9">
-        <v>43.475999999999999</v>
-      </c>
-      <c r="H58" s="9">
-        <v>-8.2859999999999996</v>
+      <c r="G58" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="H58" s="8">
+        <v>-6.206542</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>15</v>
@@ -2296,202 +2399,206 @@
         <v>16</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
-        <v>92</v>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="9">
-        <v>43.475999999999999</v>
-      </c>
-      <c r="H59" s="9">
-        <v>-8.2859999999999996</v>
+        <v>93</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G59" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="H59" s="8">
+        <v>-6.206542</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L59" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L59" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="9">
-        <v>43.475999999999999</v>
-      </c>
-      <c r="H60" s="9">
-        <v>-8.2859999999999996</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L60" s="7" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G61" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="H61" s="8">
+        <v>-6.206542</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L61" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="9">
-        <v>43.475999999999999</v>
-      </c>
-      <c r="H61" s="9">
-        <v>-8.2859999999999996</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L61" s="7" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F62" s="4"/>
-      <c r="I62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F63" s="4"/>
-      <c r="I63" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K63" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F64" s="4"/>
-      <c r="I64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K64" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="4"/>
-      <c r="F65" s="4"/>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K65" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F68" s="4"/>
-      <c r="G68" s="11">
-        <v>18.47</v>
-      </c>
-      <c r="H68" s="11">
-        <v>-66.126000000000005</v>
+      <c r="K66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G67" s="14">
+        <v>19.1738</v>
+      </c>
+      <c r="H67" s="14">
+        <v>-96.1342</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="14">
+        <v>19.1738</v>
+      </c>
+      <c r="H68" s="14">
+        <v>-96.1342</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>15</v>
@@ -2499,147 +2606,96 @@
       <c r="J68" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K68" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L68" s="7" t="s">
+      <c r="L68" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F69" s="4"/>
-      <c r="G69" s="11">
-        <v>18.47</v>
-      </c>
-      <c r="H69" s="11">
-        <v>-66.126000000000005</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F70" s="4"/>
-      <c r="G70" s="11">
-        <v>18.47</v>
-      </c>
-      <c r="H70" s="11">
-        <v>-66.126000000000005</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L70" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
-        <v>104</v>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F71" s="4"/>
-      <c r="I71" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G71" s="16">
+        <v>-52.0667</v>
+      </c>
+      <c r="H71" s="16">
+        <v>-66.7006</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
       <c r="K71" s="7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
-        <v>105</v>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F72" s="4"/>
-      <c r="G72" s="9">
-        <v>23.159700000000001</v>
-      </c>
-      <c r="H72" s="9">
-        <v>-82.353300000000004</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G72" s="16">
+        <v>-50.8631</v>
+      </c>
+      <c r="H72" s="16">
+        <v>-64.4367</v>
+      </c>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
       <c r="K72" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F74" s="4"/>
-      <c r="G74" s="9">
-        <v>23.159700000000001</v>
-      </c>
-      <c r="H74" s="9">
-        <v>-82.353300000000004</v>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G74" s="14">
+        <v>19.1738</v>
+      </c>
+      <c r="H74" s="14">
+        <v>-96.1342</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>15</v>
@@ -2647,33 +2703,39 @@
       <c r="J74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K74" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="L74" s="7" t="s">
+      <c r="K74" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="L74" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="8"/>
-      <c r="B75" s="4"/>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
       <c r="F75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="8" t="s">
-        <v>108</v>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F76" s="4"/>
-      <c r="G76" s="9">
-        <v>19.1738</v>
-      </c>
-      <c r="H76" s="9">
-        <v>-96.134200000000007</v>
+        <v>116</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" s="18">
+        <v>43.4791</v>
+      </c>
+      <c r="H76" s="18">
+        <v>-8.2375</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>15</v>
@@ -2682,32 +2744,37 @@
         <v>16</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="8"/>
-      <c r="B77" s="4"/>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="6"/>
+      <c r="B77" s="7"/>
       <c r="F77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="8" t="s">
-        <v>110</v>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>85</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C78" s="19"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="9">
-        <v>23.159700000000001</v>
-      </c>
-      <c r="H78" s="9">
-        <v>-82.353300000000004</v>
+      <c r="G78" s="13">
+        <v>43.476</v>
+      </c>
+      <c r="H78" s="13">
+        <v>-8.286</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>15</v>
@@ -2716,1199 +2783,1659 @@
         <v>16</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="L78" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="8"/>
-      <c r="B79" s="4"/>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="6"/>
+      <c r="B79" s="7"/>
       <c r="F79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="8"/>
-      <c r="B80" s="4"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="F80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="8" t="s">
-        <v>111</v>
+      <c r="G80" s="13">
+        <v>43.476</v>
+      </c>
+      <c r="H80" s="13">
+        <v>-8.286</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F81" s="4"/>
-      <c r="G81" s="11">
-        <v>36.494199999999999</v>
-      </c>
-      <c r="H81" s="11">
-        <v>-6.2065419999999998</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" s="4" t="s">
+      <c r="G81" s="13">
+        <v>43.476</v>
+      </c>
+      <c r="H81" s="13">
+        <v>-8.286</v>
+      </c>
+      <c r="I81" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="8" t="s">
-        <v>113</v>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F82" s="4"/>
-      <c r="G82" s="11">
-        <v>36.494199999999999</v>
-      </c>
-      <c r="H82" s="11">
-        <v>-6.2065419999999998</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" s="4" t="s">
+      <c r="G82" s="13">
+        <v>43.476</v>
+      </c>
+      <c r="H82" s="13">
+        <v>-8.286</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="4"/>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="F83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="8" t="s">
-        <v>114</v>
+      <c r="G83" s="13">
+        <v>43.476</v>
+      </c>
+      <c r="H83" s="13">
+        <v>-8.286</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L83" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G84" s="11">
-        <v>36.495516000000002</v>
-      </c>
-      <c r="H84" s="11">
-        <v>-6.1833400000000003</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="I84" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K84" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L84" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="8"/>
-      <c r="B85" s="4"/>
+      <c r="D85" s="7" t="s">
+        <v>127</v>
+      </c>
       <c r="F85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="8" t="s">
-        <v>118</v>
+      <c r="I85" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>85</v>
+        <v>116</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="F86" s="4"/>
-      <c r="G86" s="11">
-        <v>36.494199999999999</v>
-      </c>
-      <c r="H86" s="11">
-        <v>-6.2065419999999998</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" s="4" t="s">
+      <c r="I86" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="4"/>
       <c r="F87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G88" s="7">
-        <v>36.494199999999999</v>
-      </c>
-      <c r="H88" s="7">
-        <v>-6.2065419999999998</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L88" s="7" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="3"/>
+      <c r="B88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="20">
+        <v>18.47</v>
+      </c>
+      <c r="H90" s="20">
+        <v>-66.126</v>
+      </c>
+      <c r="I90" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L90" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="12" t="s">
-        <v>123</v>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G91" s="9">
-        <v>36.529800000000002</v>
-      </c>
-      <c r="H91" s="9">
-        <v>-6.2923</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J91" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="20">
+        <v>18.47</v>
+      </c>
+      <c r="H91" s="20">
+        <v>-66.126</v>
+      </c>
+      <c r="I91" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L91" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G92" s="11">
+      <c r="F92" s="4"/>
+      <c r="G92" s="20">
         <v>18.47</v>
       </c>
-      <c r="H92" s="11">
-        <v>-66.126000000000005</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J92" s="4" t="s">
+      <c r="H92" s="20">
+        <v>-66.126</v>
+      </c>
+      <c r="I92" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J92" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L92" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="12" t="s">
-        <v>129</v>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G93" s="9">
-        <v>23.159700000000001</v>
-      </c>
-      <c r="H93" s="9">
-        <v>-82.353300000000004</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="I93" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="L93" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="13">
+        <v>23.1597</v>
+      </c>
+      <c r="H94" s="13">
+        <v>-82.3533</v>
+      </c>
+      <c r="I94" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="L94" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1016" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1017" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1018" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="3"/>
+      <c r="B95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="13">
+        <v>23.1597</v>
+      </c>
+      <c r="H96" s="13">
+        <v>-82.3533</v>
+      </c>
+      <c r="I96" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="21"/>
+      <c r="B97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="13">
+        <v>19.1738</v>
+      </c>
+      <c r="H98" s="13">
+        <v>-96.1342</v>
+      </c>
+      <c r="I98" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="21"/>
+      <c r="B99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="13">
+        <v>23.1597</v>
+      </c>
+      <c r="H100" s="13">
+        <v>-82.3533</v>
+      </c>
+      <c r="I100" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J100" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="21"/>
+      <c r="B101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="21"/>
+      <c r="B102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F103" s="4"/>
+      <c r="G103" s="20">
+        <v>36.4942</v>
+      </c>
+      <c r="H103" s="20">
+        <v>-6.206542</v>
+      </c>
+      <c r="I103" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="20">
+        <v>36.4942</v>
+      </c>
+      <c r="H104" s="20">
+        <v>-6.206542</v>
+      </c>
+      <c r="I104" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="3"/>
+      <c r="B105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G106" s="20">
+        <v>36.495516</v>
+      </c>
+      <c r="H106" s="20">
+        <v>-6.18334</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J106" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="21"/>
+      <c r="B107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="20">
+        <v>36.4942</v>
+      </c>
+      <c r="H108" s="20">
+        <v>-6.206542</v>
+      </c>
+      <c r="I108" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L108" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="3"/>
+      <c r="B109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G110" s="11">
+        <v>36.4942</v>
+      </c>
+      <c r="H110" s="11">
+        <v>-6.206542</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L110" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G113" s="13">
+        <v>36.5298</v>
+      </c>
+      <c r="H113" s="13">
+        <v>-6.2923</v>
+      </c>
+      <c r="I113" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J113" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G114" s="20">
+        <v>18.47</v>
+      </c>
+      <c r="H114" s="20">
+        <v>-66.126</v>
+      </c>
+      <c r="I114" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G115" s="13">
+        <v>23.1597</v>
+      </c>
+      <c r="H115" s="13">
+        <v>-82.3533</v>
+      </c>
+      <c r="I115" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J115" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/lat_claude.xlsx
+++ b/lat_claude.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YUqHA3DHMydyRE56dyeACfOdA3kyMUg9AI+rpOrThlw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gC4BxCcIZKl+n7YHV0+fl8HSSkIzrhnOBjkhYgr7nMs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="179">
   <si>
     <t>fecha</t>
   </si>
@@ -24,6 +24,9 @@
     <t>id_buque</t>
   </si>
   <si>
+    <t>nombre_buque</t>
+  </si>
+  <si>
     <t>id_escuadra</t>
   </si>
   <si>
@@ -261,6 +264,9 @@
     <t>BUQ00047</t>
   </si>
   <si>
+    <t xml:space="preserve">San Pedro de Alcántara </t>
+  </si>
+  <si>
     <t>RUT0029</t>
   </si>
   <si>
@@ -300,6 +306,9 @@
     <t>BUQ00046</t>
   </si>
   <si>
+    <t>Peruano</t>
+  </si>
+  <si>
     <t>Descargando cargamento</t>
   </si>
   <si>
@@ -321,9 +330,15 @@
     <t>BUQ00023</t>
   </si>
   <si>
+    <t>Venus</t>
+  </si>
+  <si>
     <t>15/12/1785</t>
   </si>
   <si>
+    <t>Astuto</t>
+  </si>
+  <si>
     <t>16/12/1785</t>
   </si>
   <si>
@@ -342,33 +357,78 @@
     <t>06/01/1786</t>
   </si>
   <si>
+    <t>16/3/1786</t>
+  </si>
+  <si>
+    <t>BUQ00091</t>
+  </si>
+  <si>
+    <t>Santa María de la Cabeza</t>
+  </si>
+  <si>
+    <t>RUT0026</t>
+  </si>
+  <si>
+    <t>Destino Cádiz de regreso de expedición científica</t>
+  </si>
+  <si>
     <t>17/3/1786</t>
   </si>
   <si>
-    <t>BUQ00091</t>
-  </si>
-  <si>
-    <t>RUT0026</t>
-  </si>
-  <si>
-    <t>Destino Cádiz de regreso de expedición científica</t>
-  </si>
-  <si>
     <t>18/3/1786</t>
   </si>
   <si>
+    <t>19/3/1786</t>
+  </si>
+  <si>
+    <t>20/3/1786</t>
+  </si>
+  <si>
+    <t>4/4/1786</t>
+  </si>
+  <si>
+    <t>BUQ00045</t>
+  </si>
+  <si>
+    <t>América</t>
+  </si>
+  <si>
+    <t>RUT0031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destino Cádiz </t>
+  </si>
+  <si>
     <t>24/04/1786</t>
   </si>
   <si>
     <t>Esperando órdenes del Virrey</t>
   </si>
   <si>
+    <t>8/6/1786</t>
+  </si>
+  <si>
+    <t>22/6/1786</t>
+  </si>
+  <si>
+    <t>17/7/1786</t>
+  </si>
+  <si>
+    <t>15/8/1786</t>
+  </si>
+  <si>
+    <t>25/8/1786</t>
+  </si>
+  <si>
     <t>7/12/1786</t>
   </si>
   <si>
     <t>BUQ00034</t>
   </si>
   <si>
+    <t>Santa Rita</t>
+  </si>
+  <si>
     <t>INF018</t>
   </si>
   <si>
@@ -472,6 +532,9 @@
   </si>
   <si>
     <t>BUQ00028</t>
+  </si>
+  <si>
+    <t>Castilla</t>
   </si>
   <si>
     <t>RUT0022</t>
@@ -501,7 +564,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -533,6 +596,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -573,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -601,6 +669,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -608,18 +679,36 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -844,9 +933,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="11.13"/>
-    <col customWidth="1" min="5" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="6" width="15.25"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="10.0"/>
+    <col customWidth="1" min="7" max="7" width="15.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -862,13 +951,13 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -886,28 +975,29 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="5">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5">
         <v>-20.5333</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="5">
         <v>-30.5167</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>16</v>
@@ -918,28 +1008,29 @@
       <c r="L2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="5">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5">
         <v>-20.5333</v>
       </c>
-      <c r="H3" s="5">
+      <c r="I3" s="5">
         <v>-30.5167</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>16</v>
@@ -950,1180 +1041,1220 @@
       <c r="L3" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="M3" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="5">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5">
         <v>36.43333</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>-6.62834</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>22</v>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="5">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
         <v>35.63472</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>-7.63779</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="M5" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="5">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
         <v>34.36833</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>-8.90446</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="M6" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="5">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
         <v>33.53333</v>
       </c>
-      <c r="H7" s="5">
+      <c r="I7" s="5">
         <v>-9.97112</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="M7" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="5">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5">
         <v>32.60833</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>-10.96279</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="M8" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5">
         <v>36.38333</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>-6.65557</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
-        <v>22</v>
+      <c r="K9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="5">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
         <v>35.73333</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>-7.5389</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5">
+        <v>34.86667</v>
+      </c>
+      <c r="I11" s="5">
+        <v>-8.70557</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5">
-        <v>34.86667</v>
-      </c>
-      <c r="H11" s="5">
-        <v>-8.70557</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>25</v>
+      <c r="M11" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5">
         <v>34.03333</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>-9.85557</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5">
         <v>33.63333</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>-10.17223</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5">
         <v>32.9</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <v>-10.65557</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
         <v>32.48333</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>-10.92223</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5">
         <v>32.18333</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>-12.57223</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5">
         <v>30.8333</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>-14.22223</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5">
         <v>29.25</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <v>-16.00557</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5">
         <v>27.5</v>
       </c>
-      <c r="H19" s="5">
+      <c r="I19" s="5">
         <v>-17.2889</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5">
         <v>-12.0611</v>
       </c>
-      <c r="H20" s="5">
+      <c r="I20" s="5">
         <v>-77.1469</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>18</v>
+      <c r="K20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4">
         <v>-12.2</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <v>-79.5</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J21" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4">
+        <v>-13.3</v>
+      </c>
+      <c r="I22" s="4">
+        <v>-81.13337</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4">
-        <v>-13.3</v>
-      </c>
-      <c r="H22" s="4">
-        <v>-81.13337</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>25</v>
+      <c r="M22" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="4">
+      <c r="G23" s="4"/>
+      <c r="H23" s="4">
         <v>-13.85</v>
       </c>
-      <c r="H23" s="4">
+      <c r="I23" s="4">
         <v>-81.8667</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J23" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F24" s="4"/>
-      <c r="G24" s="4">
+      <c r="G24" s="4"/>
+      <c r="H24" s="4">
         <v>-15.21666</v>
       </c>
-      <c r="H24" s="4">
+      <c r="I24" s="4">
         <v>-83.45</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J24" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="4">
+      <c r="G25" s="4"/>
+      <c r="H25" s="4">
         <v>-16.4</v>
       </c>
-      <c r="H25" s="4">
+      <c r="I25" s="4">
         <v>-84.8333</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J25" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F26" s="4"/>
-      <c r="G26" s="4">
+      <c r="G26" s="4"/>
+      <c r="H26" s="4">
         <v>-17.5333</v>
       </c>
-      <c r="H26" s="4">
+      <c r="I26" s="4">
         <v>-86.5167</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J26" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F27" s="4"/>
-      <c r="G27" s="4">
+      <c r="G27" s="4"/>
+      <c r="H27" s="4">
         <v>-18.1333</v>
       </c>
-      <c r="H27" s="4">
+      <c r="I27" s="4">
         <v>-87.55</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J27" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F28" s="4"/>
-      <c r="G28" s="4">
+      <c r="G28" s="4"/>
+      <c r="H28" s="4">
         <v>-20.5167</v>
       </c>
-      <c r="H28" s="4">
+      <c r="I28" s="4">
         <v>-88.4667</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J28" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>15</v>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>15</v>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="4">
+      <c r="G31" s="4"/>
+      <c r="H31" s="4">
         <v>-25.6167</v>
       </c>
-      <c r="H31" s="4">
+      <c r="I31" s="4">
         <v>-89.5667</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J31" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="4"/>
+        <v>60</v>
+      </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4">
+      <c r="G32" s="4"/>
+      <c r="H32" s="4">
         <v>36.5298</v>
       </c>
-      <c r="H32" s="4">
+      <c r="I32" s="4">
         <v>-6.2923</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L32" s="4" t="s">
-        <v>18</v>
+      <c r="K32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4">
+      <c r="G33" s="4"/>
+      <c r="H33" s="4">
         <v>36.41667</v>
       </c>
-      <c r="H33" s="4">
+      <c r="I33" s="4">
         <v>-6.60557</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J33" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4">
+      <c r="G34" s="4"/>
+      <c r="H34" s="4">
         <v>35.91667</v>
       </c>
-      <c r="H34" s="4">
+      <c r="I34" s="4">
         <v>-7.4389</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J34" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4">
+      <c r="G35" s="4"/>
+      <c r="H35" s="4">
         <v>36.675</v>
       </c>
-      <c r="H35" s="4">
+      <c r="I35" s="4">
         <v>-7.08057</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4">
+      <c r="G36" s="4"/>
+      <c r="H36" s="4">
         <v>36.66667</v>
       </c>
-      <c r="H36" s="4">
+      <c r="I36" s="4">
         <v>-7.5389</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J36" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4">
         <v>36.60833</v>
       </c>
-      <c r="H37" s="4">
+      <c r="I37" s="4">
         <v>-8.15558</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J37" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="4">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4">
         <v>36.86667</v>
       </c>
-      <c r="H38" s="4">
+      <c r="I38" s="4">
         <v>-9.0889</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J38" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="G39" s="4">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="H39" s="4">
         <v>36.61667</v>
       </c>
-      <c r="H39" s="4">
+      <c r="I39" s="4">
         <v>-10.59723</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J39" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="G40" s="4">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="H40" s="4">
         <v>36.51667</v>
       </c>
-      <c r="H40" s="4">
+      <c r="I40" s="4">
         <v>-11.57223</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G45" s="4">
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="4">
         <v>36.818056</v>
       </c>
-      <c r="H45" s="4">
+      <c r="I45" s="4">
         <v>-8.563611</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J45" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -2132,361 +2263,405 @@
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="F46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B47" s="7"/>
-      <c r="C47" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="C47" s="7"/>
       <c r="D47" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="8">
+      <c r="G47" s="4"/>
+      <c r="H47" s="8">
         <v>-12.0611</v>
       </c>
-      <c r="H47" s="8">
+      <c r="I47" s="8">
         <v>-77.1469</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>25</v>
+      <c r="K47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B48" s="7" t="s">
         <v>80</v>
       </c>
+      <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="10">
+        <v>-42.61667</v>
+      </c>
+      <c r="I48" s="10">
+        <v>-76.1923</v>
+      </c>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="10">
+      <c r="C49" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="10">
         <v>-42.61667</v>
       </c>
-      <c r="H48" s="10">
+      <c r="I49" s="10">
         <v>-76.1923</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="8">
-        <v>-36.7382</v>
-      </c>
-      <c r="H49" s="8">
-        <v>-73.1388</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L49" s="11" t="s">
-        <v>18</v>
+      <c r="M49" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="4"/>
+      <c r="B50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="7"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="8">
-        <v>-22.881353</v>
-      </c>
+      <c r="G50" s="4"/>
       <c r="H50" s="8">
-        <v>-43.182717</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>15</v>
+        <v>-36.7382</v>
+      </c>
+      <c r="I50" s="8">
+        <v>-73.1388</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L50" s="11" t="s">
-        <v>18</v>
+      <c r="K50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="12"/>
+      <c r="A51" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="D51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="8">
+        <v>-22.881353</v>
+      </c>
+      <c r="I51" s="8">
+        <v>-43.182717</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>80</v>
-      </c>
+      <c r="A52" s="13"/>
+      <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="D52" s="7"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="8">
-        <v>-36.7382</v>
-      </c>
-      <c r="H52" s="8">
-        <v>-73.1388</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="8">
+        <v>-36.7382</v>
+      </c>
+      <c r="I53" s="8">
+        <v>-73.1388</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="7" t="s">
+      <c r="M53" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G53" s="8">
+      <c r="C54" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" s="8">
         <v>-12.0611</v>
       </c>
-      <c r="H53" s="8">
+      <c r="I54" s="8">
         <v>-77.1469</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-    </row>
+      <c r="J54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>77</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="13">
-        <v>36.5298</v>
-      </c>
-      <c r="H57" s="13">
-        <v>-6.2923</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="14">
+        <v>36.5298</v>
+      </c>
+      <c r="I58" s="14">
+        <v>-6.2923</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M58" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="H58" s="8">
-        <v>-6.206542</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L58" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
+      <c r="C59" s="15" t="s">
+        <v>96</v>
+      </c>
       <c r="E59" s="4"/>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="I59" s="8">
+        <v>-6.206542</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G59" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="H59" s="8">
-        <v>-6.206542</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H60" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="I60" s="8">
+        <v>-6.206542</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M60" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>100</v>
-      </c>
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" s="8">
+      <c r="F61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="8">
         <v>36.4942</v>
       </c>
-      <c r="H61" s="8">
+      <c r="I62" s="8">
         <v>-6.206542</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
+      <c r="J62" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M62" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
@@ -2494,1033 +2669,1468 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="G63" s="4"/>
+      <c r="F63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="F64" s="4"/>
       <c r="H64" s="4"/>
-      <c r="I64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4" t="s">
-        <v>103</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="F65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
+      <c r="J65" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K65" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
+      <c r="A66" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>106</v>
+      </c>
       <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="E66" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
-      <c r="K66" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="K66" s="4"/>
       <c r="L66" s="4" t="s">
-        <v>25</v>
+        <v>109</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G67" s="14">
-        <v>19.1738</v>
-      </c>
-      <c r="H67" s="14">
-        <v>-96.1342</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L67" s="11" t="s">
-        <v>90</v>
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="14">
+      <c r="H68" s="17">
         <v>19.1738</v>
       </c>
-      <c r="H68" s="14">
+      <c r="I68" s="17">
         <v>-96.1342</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J68" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L68" s="11" t="s">
-        <v>18</v>
+      <c r="K68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M68" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H69" s="17">
+        <v>19.1738</v>
+      </c>
+      <c r="I69" s="17">
+        <v>-96.1342</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M69" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3"/>
-      <c r="B70" s="4"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
+      <c r="A70" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G71" s="16">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H72" s="14">
+        <v>-52.33039</v>
+      </c>
+      <c r="I72" s="14">
+        <v>-68.3444</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H73" s="19">
         <v>-52.0667</v>
       </c>
-      <c r="H71" s="16">
+      <c r="I73" s="19">
         <v>-66.7006</v>
       </c>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G72" s="16">
+      <c r="J73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H74" s="19">
         <v>-50.8631</v>
       </c>
-      <c r="H72" s="16">
+      <c r="I74" s="19">
         <v>-64.4367</v>
       </c>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3"/>
-      <c r="B73" s="4"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G74" s="14">
-        <v>19.1738</v>
-      </c>
-      <c r="H74" s="14">
-        <v>-96.1342</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L74" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="7"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
+      <c r="C75" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H75" s="19">
+        <v>-49.475</v>
+      </c>
+      <c r="I75" s="19">
+        <v>-62.2117</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="E76" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" s="19">
+        <v>-48.7006</v>
+      </c>
+      <c r="I76" s="19">
+        <v>-61.0917</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G76" s="18">
-        <v>43.4791</v>
-      </c>
-      <c r="H76" s="18">
-        <v>-8.2375</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K76" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="L76" s="7" t="s">
-        <v>18</v>
+      <c r="M76" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="7"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="H77" s="17"/>
       <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="19"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="13">
-        <v>43.476</v>
-      </c>
-      <c r="H78" s="13">
-        <v>-8.286</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>15</v>
+      <c r="A78" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H78" s="14">
+        <v>-12.0611</v>
+      </c>
+      <c r="I78" s="14">
+        <v>-77.1469</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K78" s="7" t="s">
-        <v>120</v>
+      <c r="K78" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>18</v>
+        <v>126</v>
+      </c>
+      <c r="M78" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="7"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="H79" s="17"/>
       <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="13">
-        <v>43.476</v>
-      </c>
-      <c r="H80" s="13">
-        <v>-8.286</v>
-      </c>
-      <c r="I80" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L80" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="13">
-        <v>43.476</v>
-      </c>
-      <c r="H81" s="13">
-        <v>-8.286</v>
-      </c>
-      <c r="I81" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L81" s="7" t="s">
-        <v>18</v>
+      <c r="A81" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H81" s="17">
+        <v>19.1738</v>
+      </c>
+      <c r="I81" s="17">
+        <v>-96.1342</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="M81" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="13">
-        <v>43.476</v>
-      </c>
-      <c r="H82" s="13">
-        <v>-8.286</v>
-      </c>
-      <c r="I82" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K82" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L82" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A82" s="6"/>
+      <c r="B82" s="7"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="22"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="13">
-        <v>43.476</v>
-      </c>
-      <c r="H83" s="13">
-        <v>-8.286</v>
-      </c>
-      <c r="I83" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="7" t="s">
-        <v>122</v>
+      <c r="G83" s="4"/>
+      <c r="H83" s="24">
+        <v>-39.0</v>
+      </c>
+      <c r="I83" s="24">
+        <v>-37.6389</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>18</v>
+        <v>126</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B84" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="H84" s="24">
+        <v>-18.0</v>
+      </c>
+      <c r="I84" s="24">
+        <v>-27.6389</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F84" s="4"/>
-      <c r="I84" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="L84" s="4" t="s">
-        <v>25</v>
+      <c r="M84" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F85" s="4"/>
-      <c r="I85" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>25</v>
+        <v>131</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="I85" s="24">
+        <v>-32.2222</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F86" s="4"/>
-      <c r="I86" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="L86" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A86" s="6"/>
+      <c r="B86" s="7"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3"/>
-      <c r="B87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
+      <c r="A87" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="14">
+        <v>36.5298</v>
+      </c>
+      <c r="I87" s="14">
+        <v>-6.2923</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L87" s="7"/>
+      <c r="M87" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3"/>
-      <c r="B88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
+      <c r="A88" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H88" s="8">
+        <v>36.4942</v>
+      </c>
+      <c r="I88" s="14">
+        <v>-6.206542</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L88" s="7"/>
+      <c r="M88" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="3"/>
-      <c r="B89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="7"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="22"/>
+      <c r="L89" s="7"/>
+      <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F90" s="4"/>
-      <c r="G90" s="20">
-        <v>18.47</v>
-      </c>
-      <c r="H90" s="20">
-        <v>-66.126</v>
-      </c>
-      <c r="I90" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J90" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K90" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H90" s="24">
+        <v>43.4791</v>
+      </c>
+      <c r="I90" s="24">
+        <v>-8.2375</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>18</v>
+        <v>138</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="20">
-        <v>18.47</v>
-      </c>
-      <c r="H91" s="20">
-        <v>-66.126</v>
-      </c>
-      <c r="I91" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J91" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L91" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A91" s="6"/>
+      <c r="B91" s="7"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="22"/>
+      <c r="K91" s="22"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="4"/>
-      <c r="G92" s="20">
-        <v>18.47</v>
-      </c>
-      <c r="H92" s="20">
-        <v>-66.126</v>
-      </c>
-      <c r="I92" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J92" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="26"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="14">
+        <v>43.476</v>
+      </c>
+      <c r="I92" s="14">
+        <v>-8.286</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>18</v>
+        <v>140</v>
+      </c>
+      <c r="M92" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F93" s="4"/>
-      <c r="I93" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K93" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A93" s="6"/>
+      <c r="B93" s="7"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="22"/>
+      <c r="K93" s="22"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B94" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="13">
-        <v>23.1597</v>
-      </c>
-      <c r="H94" s="13">
-        <v>-82.3533</v>
-      </c>
-      <c r="I94" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="7" t="s">
-        <v>137</v>
+      <c r="G94" s="4"/>
+      <c r="H94" s="14">
+        <v>43.476</v>
+      </c>
+      <c r="I94" s="14">
+        <v>-8.286</v>
+      </c>
+      <c r="J94" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>18</v>
+        <v>142</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="3"/>
-      <c r="B95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
+      <c r="A95" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="14">
+        <v>43.476</v>
+      </c>
+      <c r="I95" s="14">
+        <v>-8.286</v>
+      </c>
+      <c r="J95" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="M95" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="13">
-        <v>23.1597</v>
-      </c>
-      <c r="H96" s="13">
-        <v>-82.3533</v>
-      </c>
-      <c r="I96" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J96" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K96" s="11" t="s">
-        <v>114</v>
+        <v>135</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="14">
+        <v>43.476</v>
+      </c>
+      <c r="I96" s="14">
+        <v>-8.286</v>
+      </c>
+      <c r="J96" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K96" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>18</v>
+        <v>142</v>
+      </c>
+      <c r="M96" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="21"/>
-      <c r="B97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="A97" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="14">
+        <v>43.476</v>
+      </c>
+      <c r="I97" s="14">
+        <v>-8.286</v>
+      </c>
+      <c r="J97" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L97" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F98" s="4"/>
-      <c r="G98" s="13">
-        <v>19.1738</v>
-      </c>
-      <c r="H98" s="13">
-        <v>-96.1342</v>
-      </c>
-      <c r="I98" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J98" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="J98" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>18</v>
+        <v>148</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="21"/>
-      <c r="B99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="A99" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="J99" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F100" s="4"/>
-      <c r="G100" s="13">
-        <v>23.1597</v>
-      </c>
-      <c r="H100" s="13">
-        <v>-82.3533</v>
-      </c>
-      <c r="I100" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J100" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K100" s="11" t="s">
-        <v>114</v>
+        <v>135</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G100" s="4"/>
+      <c r="J100" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>18</v>
+        <v>148</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="21"/>
+      <c r="A101" s="3"/>
       <c r="B101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="I101" s="4"/>
+      <c r="G101" s="4"/>
       <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="21"/>
+      <c r="A102" s="3"/>
       <c r="B102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="I102" s="4"/>
+      <c r="G102" s="4"/>
       <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="20">
-        <v>36.4942</v>
-      </c>
-      <c r="H103" s="20">
-        <v>-6.206542</v>
-      </c>
-      <c r="I103" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J103" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K103" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A103" s="3"/>
+      <c r="B103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F104" s="4"/>
-      <c r="G104" s="20">
-        <v>36.4942</v>
-      </c>
-      <c r="H104" s="20">
-        <v>-6.206542</v>
-      </c>
-      <c r="I104" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J104" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K104" s="7" t="s">
-        <v>94</v>
+        <v>135</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G104" s="4"/>
+      <c r="H104" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I104" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J104" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>18</v>
+        <v>152</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
-      <c r="F105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
+      <c r="A105" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G105" s="4"/>
+      <c r="H105" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I105" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J105" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K105" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="M105" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G106" s="20">
-        <v>36.495516</v>
-      </c>
-      <c r="H106" s="20">
-        <v>-6.18334</v>
-      </c>
-      <c r="I106" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J106" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K106" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G106" s="4"/>
+      <c r="H106" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I106" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J106" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L106" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="M106" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E107" s="7" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="21"/>
-      <c r="B107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="J107" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K107" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F108" s="4"/>
-      <c r="G108" s="20">
-        <v>36.4942</v>
-      </c>
-      <c r="H108" s="20">
-        <v>-6.206542</v>
-      </c>
-      <c r="I108" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J108" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K108" s="7" t="s">
-        <v>120</v>
+        <v>135</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="14">
+        <v>23.1597</v>
+      </c>
+      <c r="I108" s="14">
+        <v>-82.3533</v>
+      </c>
+      <c r="J108" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" s="22" t="s">
+        <v>17</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>18</v>
+        <v>157</v>
+      </c>
+      <c r="M108" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="I109" s="4"/>
+      <c r="G109" s="4"/>
       <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G110" s="11">
+      <c r="A110" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="14">
+        <v>23.1597</v>
+      </c>
+      <c r="I110" s="14">
+        <v>-82.3533</v>
+      </c>
+      <c r="J110" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K110" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="M110" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="28"/>
+      <c r="B111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G112" s="4"/>
+      <c r="H112" s="14">
+        <v>19.1738</v>
+      </c>
+      <c r="I112" s="14">
+        <v>-96.1342</v>
+      </c>
+      <c r="J112" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K112" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="M112" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="28"/>
+      <c r="B113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G114" s="4"/>
+      <c r="H114" s="14">
+        <v>23.1597</v>
+      </c>
+      <c r="I114" s="14">
+        <v>-82.3533</v>
+      </c>
+      <c r="J114" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L114" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="M114" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="28"/>
+      <c r="B115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="28"/>
+      <c r="B116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="27">
         <v>36.4942</v>
       </c>
-      <c r="H110" s="11">
+      <c r="I117" s="27">
         <v>-6.206542</v>
       </c>
-      <c r="I110" s="4" t="s">
+      <c r="J117" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L117" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J110" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L110" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G113" s="13">
-        <v>36.5298</v>
-      </c>
-      <c r="H113" s="13">
-        <v>-6.2923</v>
-      </c>
-      <c r="I113" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J113" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K113" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="L113" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G114" s="20">
-        <v>18.47</v>
-      </c>
-      <c r="H114" s="20">
-        <v>-66.126</v>
-      </c>
-      <c r="I114" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J114" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K114" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G115" s="13">
-        <v>23.1597</v>
-      </c>
-      <c r="H115" s="13">
-        <v>-82.3533</v>
-      </c>
-      <c r="I115" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J115" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K115" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
+      <c r="M117" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G118" s="4"/>
+      <c r="H118" s="27">
+        <v>36.4942</v>
+      </c>
+      <c r="I118" s="27">
+        <v>-6.206542</v>
+      </c>
+      <c r="J118" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K118" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M118" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="3"/>
+      <c r="B119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H120" s="27">
+        <v>36.495516</v>
+      </c>
+      <c r="I120" s="27">
+        <v>-6.18334</v>
+      </c>
+      <c r="J120" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K120" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M120" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="28"/>
+      <c r="B121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G122" s="4"/>
+      <c r="H122" s="27">
+        <v>36.4942</v>
+      </c>
+      <c r="I122" s="27">
+        <v>-6.206542</v>
+      </c>
+      <c r="J122" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K122" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="M122" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="3"/>
+      <c r="B123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H124" s="12">
+        <v>36.4942</v>
+      </c>
+      <c r="I124" s="12">
+        <v>-6.206542</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K124" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M124" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="125" ht="15.75" customHeight="1"/>
     <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H127" s="14">
+        <v>36.5298</v>
+      </c>
+      <c r="I127" s="14">
+        <v>-6.2923</v>
+      </c>
+      <c r="J127" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K127" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L127" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H128" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I128" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J128" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K128" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L128" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="M128" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H129" s="14">
+        <v>23.1597</v>
+      </c>
+      <c r="I129" s="14">
+        <v>-82.3533</v>
+      </c>
+      <c r="J129" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K129" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="M129" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="130" ht="15.75" customHeight="1"/>
     <row r="131" ht="15.75" customHeight="1"/>
     <row r="132" ht="15.75" customHeight="1"/>
@@ -4432,6 +5042,20 @@
     <row r="1038" ht="15.75" customHeight="1"/>
     <row r="1039" ht="15.75" customHeight="1"/>
     <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1"/>
+    <row r="1047" ht="15.75" customHeight="1"/>
+    <row r="1048" ht="15.75" customHeight="1"/>
+    <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/lat_claude.xlsx
+++ b/lat_claude.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gC4BxCcIZKl+n7YHV0+fl8HSSkIzrhnOBjkhYgr7nMs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6+ggSBXlkxftV/9fO73DxNILGvT3tzeWQazyqmER1AE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="203">
   <si>
     <t>fecha</t>
   </si>
@@ -57,6 +57,42 @@
     <t>navegacion</t>
   </si>
   <si>
+    <t>2/6/1758</t>
+  </si>
+  <si>
+    <t>ESC0008</t>
+  </si>
+  <si>
+    <t>RUT0035</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>armado</t>
+  </si>
+  <si>
+    <t>Destino Cádiz, patrulla contra corsarios argelinos</t>
+  </si>
+  <si>
+    <t>partida</t>
+  </si>
+  <si>
+    <t>8/6/1758</t>
+  </si>
+  <si>
+    <t>BAT00004</t>
+  </si>
+  <si>
+    <t>En combate</t>
+  </si>
+  <si>
+    <t>15/6/1758</t>
+  </si>
+  <si>
+    <t>arribada</t>
+  </si>
+  <si>
     <t>04/04/1774</t>
   </si>
   <si>
@@ -66,12 +102,6 @@
     <t>ESC0004</t>
   </si>
   <si>
-    <t>activo</t>
-  </si>
-  <si>
-    <t>armado</t>
-  </si>
-  <si>
     <t>Expedición científica</t>
   </si>
   <si>
@@ -243,9 +273,6 @@
     <t>BAT00001</t>
   </si>
   <si>
-    <t>En combate</t>
-  </si>
-  <si>
     <t>14/4/1784</t>
   </si>
   <si>
@@ -288,15 +315,9 @@
     <t>Destino Callao</t>
   </si>
   <si>
-    <t>partida</t>
-  </si>
-  <si>
     <t>15/09/1784</t>
   </si>
   <si>
-    <t>arribada</t>
-  </si>
-  <si>
     <t>21/2/1785</t>
   </si>
   <si>
@@ -405,19 +426,70 @@
     <t>Esperando órdenes del Virrey</t>
   </si>
   <si>
+    <t>20/5/1786</t>
+  </si>
+  <si>
+    <t>BUQ00139</t>
+  </si>
+  <si>
+    <t>Miño</t>
+  </si>
+  <si>
+    <t>RUT0033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destino Constantinopla, transporte de embajada marroquí </t>
+  </si>
+  <si>
     <t>8/6/1786</t>
   </si>
   <si>
+    <t>19/6/1786</t>
+  </si>
+  <si>
+    <t>Destino Constantinopla, transporte de embajada marroquí. Parada para aguada</t>
+  </si>
+  <si>
     <t>22/6/1786</t>
   </si>
   <si>
+    <t>15/7/1786</t>
+  </si>
+  <si>
+    <t>Destino Constantinopla, transporte de embajada marroquí. Parada para pedir permisos para arribar a puerto</t>
+  </si>
+  <si>
     <t>17/7/1786</t>
   </si>
   <si>
+    <t>31/7/1786</t>
+  </si>
+  <si>
+    <t>Constantinopla</t>
+  </si>
+  <si>
     <t>15/8/1786</t>
   </si>
   <si>
+    <t>18/8/1786</t>
+  </si>
+  <si>
+    <t>RUT0034</t>
+  </si>
+  <si>
+    <t>Destino Cádiz</t>
+  </si>
+  <si>
     <t>25/8/1786</t>
+  </si>
+  <si>
+    <t>23/9/1786</t>
+  </si>
+  <si>
+    <t>Destino Cádiz. Hace parada para pasar cuarentena antes de arribar a Cádiz</t>
+  </si>
+  <si>
+    <t>31/12/1786</t>
   </si>
   <si>
     <t>7/12/1786</t>
@@ -561,8 +633,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -655,15 +727,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -673,11 +754,8 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -685,26 +763,20 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -980,57 +1052,39 @@
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="5">
-        <v>-20.5333</v>
-      </c>
-      <c r="I2" s="5">
-        <v>-30.5167</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="5">
-        <v>-20.5333</v>
-      </c>
-      <c r="I3" s="5">
-        <v>-30.5167</v>
+      <c r="H3" s="8">
+        <v>37.585</v>
+      </c>
+      <c r="I3" s="8">
+        <v>-0.968</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>16</v>
@@ -1038,59 +1092,67 @@
       <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
+      <c r="A4" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="8">
+        <v>37.1718</v>
+      </c>
+      <c r="I4" s="8">
+        <v>4.5003</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5">
-        <v>36.43333</v>
-      </c>
-      <c r="I4" s="5">
-        <v>-6.62834</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5">
-        <v>35.63472</v>
-      </c>
-      <c r="I5" s="5">
-        <v>-7.63779</v>
+      <c r="H5" s="8">
+        <v>36.5298</v>
+      </c>
+      <c r="I5" s="8">
+        <v>-6.2923</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>16</v>
@@ -1098,61 +1160,45 @@
       <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>26</v>
+      <c r="L5" s="4"/>
+      <c r="M5" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5">
-        <v>34.36833</v>
-      </c>
-      <c r="I6" s="5">
-        <v>-8.90446</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
-        <v>33.53333</v>
+        <v>-20.5333</v>
       </c>
       <c r="I7" s="5">
-        <v>-9.97112</v>
+        <v>-30.5167</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>16</v>
@@ -1161,29 +1207,31 @@
         <v>17</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <v>32.60833</v>
+        <v>-20.5333</v>
       </c>
       <c r="I8" s="5">
-        <v>-10.96279</v>
+        <v>-30.5167</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>16</v>
@@ -1192,31 +1240,29 @@
         <v>17</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
-        <v>36.38333</v>
+        <v>36.43333</v>
       </c>
       <c r="I9" s="5">
-        <v>-6.65557</v>
+        <v>-6.62834</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>16</v>
@@ -1226,28 +1272,26 @@
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
-        <v>35.73333</v>
+        <v>35.63472</v>
       </c>
       <c r="I10" s="5">
-        <v>-7.5389</v>
+        <v>-7.63779</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>16</v>
@@ -1256,31 +1300,29 @@
         <v>17</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <v>34.86667</v>
+        <v>34.36833</v>
       </c>
       <c r="I11" s="5">
-        <v>-8.70557</v>
+        <v>-8.90446</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>16</v>
@@ -1289,31 +1331,29 @@
         <v>17</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
-        <v>34.03333</v>
+        <v>33.53333</v>
       </c>
       <c r="I12" s="5">
-        <v>-9.85557</v>
+        <v>-9.97112</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>16</v>
@@ -1322,31 +1362,29 @@
         <v>17</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
-        <v>33.63333</v>
+        <v>32.60833</v>
       </c>
       <c r="I13" s="5">
-        <v>-10.17223</v>
+        <v>-10.96279</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>16</v>
@@ -1355,31 +1393,31 @@
         <v>17</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>32.9</v>
+        <v>36.38333</v>
       </c>
       <c r="I14" s="5">
-        <v>-10.65557</v>
+        <v>-6.65557</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>16</v>
@@ -1387,32 +1425,30 @@
       <c r="K14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
-        <v>32.48333</v>
+        <v>35.73333</v>
       </c>
       <c r="I15" s="5">
-        <v>-10.92223</v>
+        <v>-7.5389</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>16</v>
@@ -1421,31 +1457,31 @@
         <v>17</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
-        <v>32.18333</v>
+        <v>34.86667</v>
       </c>
       <c r="I16" s="5">
-        <v>-12.57223</v>
+        <v>-8.70557</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>16</v>
@@ -1454,31 +1490,31 @@
         <v>17</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
-        <v>30.8333</v>
+        <v>34.03333</v>
       </c>
       <c r="I17" s="5">
-        <v>-14.22223</v>
+        <v>-9.85557</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>16</v>
@@ -1487,31 +1523,31 @@
         <v>17</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
-        <v>29.25</v>
+        <v>33.63333</v>
       </c>
       <c r="I18" s="5">
-        <v>-16.00557</v>
+        <v>-10.17223</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>16</v>
@@ -1520,31 +1556,31 @@
         <v>17</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
-        <v>27.5</v>
+        <v>32.9</v>
       </c>
       <c r="I19" s="5">
-        <v>-17.2889</v>
+        <v>-10.65557</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>16</v>
@@ -1553,31 +1589,31 @@
         <v>17</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
-        <v>-12.0611</v>
+        <v>32.48333</v>
       </c>
       <c r="I20" s="5">
-        <v>-77.1469</v>
+        <v>-10.92223</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>16</v>
@@ -1585,29 +1621,32 @@
       <c r="K20" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="L20" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M20" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4">
-        <v>-12.2</v>
-      </c>
-      <c r="I21" s="4">
-        <v>-79.5</v>
+        <v>42</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5">
+        <v>32.18333</v>
+      </c>
+      <c r="I21" s="5">
+        <v>-12.57223</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>16</v>
@@ -1616,31 +1655,31 @@
         <v>17</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4">
-        <v>-13.3</v>
-      </c>
-      <c r="I22" s="4">
-        <v>-81.13337</v>
+        <v>42</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <v>30.8333</v>
+      </c>
+      <c r="I22" s="5">
+        <v>-14.22223</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>16</v>
@@ -1649,31 +1688,31 @@
         <v>17</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4">
-        <v>-13.85</v>
-      </c>
-      <c r="I23" s="4">
-        <v>-81.8667</v>
+        <v>42</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5">
+        <v>29.25</v>
+      </c>
+      <c r="I23" s="5">
+        <v>-16.00557</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>16</v>
@@ -1682,31 +1721,31 @@
         <v>17</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4">
-        <v>-15.21666</v>
-      </c>
-      <c r="I24" s="4">
-        <v>-83.45</v>
+        <v>42</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="I24" s="5">
+        <v>-17.2889</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>16</v>
@@ -1715,31 +1754,31 @@
         <v>17</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="I25" s="4">
-        <v>-84.8333</v>
+        <v>56</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5">
+        <v>-12.0611</v>
+      </c>
+      <c r="I25" s="5">
+        <v>-77.1469</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>16</v>
@@ -1747,32 +1786,29 @@
       <c r="K25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="M25" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4">
-        <v>-17.5333</v>
+        <v>-12.2</v>
       </c>
       <c r="I26" s="4">
-        <v>-86.5167</v>
+        <v>-79.5</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>16</v>
@@ -1781,31 +1817,31 @@
         <v>17</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4">
-        <v>-18.1333</v>
+        <v>-13.3</v>
       </c>
       <c r="I27" s="4">
-        <v>-87.55</v>
+        <v>-81.13337</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>16</v>
@@ -1814,31 +1850,31 @@
         <v>17</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4">
-        <v>-20.5167</v>
+        <v>-13.85</v>
       </c>
       <c r="I28" s="4">
-        <v>-88.4667</v>
+        <v>-81.8667</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>16</v>
@@ -1847,23 +1883,31 @@
         <v>17</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4">
+        <v>-15.21666</v>
+      </c>
+      <c r="I29" s="4">
+        <v>-83.45</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>16</v>
@@ -1872,23 +1916,31 @@
         <v>17</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-84.8333</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>16</v>
@@ -1897,31 +1949,31 @@
         <v>17</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4">
-        <v>-25.6167</v>
+        <v>-17.5333</v>
       </c>
       <c r="I31" s="4">
-        <v>-89.5667</v>
+        <v>-86.5167</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>16</v>
@@ -1930,26 +1982,31 @@
         <v>17</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4">
-        <v>36.5298</v>
+        <v>-18.1333</v>
       </c>
       <c r="I32" s="4">
-        <v>-6.2923</v>
+        <v>-87.55</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>16</v>
@@ -1957,27 +2014,32 @@
       <c r="K32" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="L32" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="M32" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="C33" s="4"/>
-      <c r="D33" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4">
-        <v>36.41667</v>
+        <v>-20.5167</v>
       </c>
       <c r="I33" s="4">
-        <v>-6.60557</v>
+        <v>-88.4667</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>16</v>
@@ -1986,29 +2048,23 @@
         <v>17</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4">
-        <v>35.91667</v>
-      </c>
-      <c r="I34" s="4">
-        <v>-7.4389</v>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>16</v>
@@ -2017,29 +2073,23 @@
         <v>17</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4">
-        <v>36.675</v>
-      </c>
-      <c r="I35" s="4">
-        <v>-7.08057</v>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>16</v>
@@ -2048,29 +2098,31 @@
         <v>17</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4">
-        <v>36.66667</v>
+        <v>-25.6167</v>
       </c>
       <c r="I36" s="4">
-        <v>-7.5389</v>
+        <v>-89.5667</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>16</v>
@@ -2079,29 +2131,26 @@
         <v>17</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4">
-        <v>36.60833</v>
+        <v>36.5298</v>
       </c>
       <c r="I37" s="4">
-        <v>-8.15558</v>
+        <v>-6.2923</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>16</v>
@@ -2109,30 +2158,27 @@
       <c r="K37" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L37" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="M37" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4">
-        <v>36.86667</v>
+        <v>36.41667</v>
       </c>
       <c r="I38" s="4">
-        <v>-9.0889</v>
+        <v>-6.60557</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>16</v>
@@ -2141,27 +2187,29 @@
         <v>17</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
       <c r="H39" s="4">
-        <v>36.61667</v>
+        <v>35.91667</v>
       </c>
       <c r="I39" s="4">
-        <v>-10.59723</v>
+        <v>-7.4389</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>16</v>
@@ -2170,27 +2218,29 @@
         <v>17</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
       <c r="H40" s="4">
-        <v>36.51667</v>
+        <v>36.675</v>
       </c>
       <c r="I40" s="4">
-        <v>-11.57223</v>
+        <v>-7.08057</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>16</v>
@@ -2199,350 +2249,424 @@
         <v>17</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4">
+        <v>36.66667</v>
+      </c>
+      <c r="I41" s="4">
+        <v>-7.5389</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4">
+        <v>36.60833</v>
+      </c>
+      <c r="I42" s="4">
+        <v>-8.15558</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4">
+        <v>36.86667</v>
+      </c>
+      <c r="I43" s="4">
+        <v>-9.0889</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="H44" s="4">
+        <v>36.61667</v>
+      </c>
+      <c r="I44" s="4">
+        <v>-10.59723</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="H45" s="4">
+        <v>36.51667</v>
+      </c>
+      <c r="I45" s="4">
+        <v>-11.57223</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H45" s="4">
+      <c r="M45" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H50" s="4">
         <v>36.818056</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I50" s="4">
         <v>-8.563611</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="8">
-        <v>-12.0611</v>
-      </c>
-      <c r="I47" s="8">
-        <v>-77.1469</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="10">
-        <v>-42.61667</v>
-      </c>
-      <c r="I48" s="10">
-        <v>-76.1923</v>
-      </c>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="10">
-        <v>-42.61667</v>
-      </c>
-      <c r="I49" s="10">
-        <v>-76.1923</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6" t="s">
+      <c r="J50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="3"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="7"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="8">
-        <v>-36.7382</v>
-      </c>
-      <c r="I50" s="8">
-        <v>-73.1388</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M50" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="8">
-        <v>-22.881353</v>
-      </c>
-      <c r="I51" s="8">
-        <v>-43.182717</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="13"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="4"/>
+      <c r="D52" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
+      <c r="H52" s="11">
+        <v>-12.0611</v>
+      </c>
+      <c r="I52" s="11">
+        <v>-77.1469</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53" s="7"/>
+      <c r="A53" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="E53" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="8">
+      <c r="H53" s="13">
+        <v>-42.61667</v>
+      </c>
+      <c r="I53" s="13">
+        <v>-76.1923</v>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="13">
+        <v>-42.61667</v>
+      </c>
+      <c r="I54" s="13">
+        <v>-76.1923</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="7"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="11">
         <v>-36.7382</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I55" s="11">
         <v>-73.1388</v>
       </c>
-      <c r="J53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="M53" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H54" s="8">
-        <v>-12.0611</v>
-      </c>
-      <c r="I54" s="8">
-        <v>-77.1469</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M54" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1"/>
+      <c r="J55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="M55" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="11">
+        <v>-22.881353</v>
+      </c>
+      <c r="I56" s="11">
+        <v>-43.182717</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M56" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
+      <c r="A57" s="16"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7" t="s">
-        <v>77</v>
-      </c>
+      <c r="A58" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="7"/>
       <c r="E58" s="7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="14">
-        <v>36.5298</v>
-      </c>
-      <c r="I58" s="14">
-        <v>-6.2923</v>
+      <c r="H58" s="11">
+        <v>-36.7382</v>
+      </c>
+      <c r="I58" s="11">
+        <v>-73.1388</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>16</v>
@@ -2550,28 +2674,31 @@
       <c r="K58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="12" t="s">
+      <c r="L58" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="I59" s="8">
-        <v>-6.206542</v>
+      <c r="H59" s="11">
+        <v>-12.0611</v>
+      </c>
+      <c r="I59" s="11">
+        <v>-77.1469</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>16</v>
@@ -2579,490 +2706,479 @@
       <c r="K59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H60" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="I60" s="8">
-        <v>-6.206542</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M60" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-    </row>
+      <c r="M59" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>104</v>
-      </c>
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H62" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="I62" s="8">
-        <v>-6.206542</v>
-      </c>
-      <c r="J62" s="4" t="s">
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="K62" s="4" t="s">
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="8">
+        <v>36.5298</v>
+      </c>
+      <c r="I63" s="8">
+        <v>-6.2923</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M63" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="M62" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="B64" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>103</v>
+      </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="11">
+        <v>36.4942</v>
+      </c>
+      <c r="I64" s="11">
+        <v>-6.206542</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>106</v>
+      <c r="B65" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H65" s="11">
+        <v>36.4942</v>
+      </c>
+      <c r="I65" s="11">
+        <v>-6.206542</v>
+      </c>
       <c r="J65" s="4" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4" t="s">
-        <v>19</v>
+        <v>108</v>
+      </c>
+      <c r="M65" s="15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>106</v>
-      </c>
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="4" t="s">
-        <v>108</v>
-      </c>
+      <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
-      <c r="L66" s="4" t="s">
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="M66" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
+      <c r="B67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>111</v>
+      </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>26</v>
+      <c r="G67" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H67" s="11">
+        <v>36.4942</v>
+      </c>
+      <c r="I67" s="11">
+        <v>-6.206542</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M67" s="15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H68" s="17">
-        <v>19.1738</v>
-      </c>
-      <c r="I68" s="17">
-        <v>-96.1342</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M68" s="12" t="s">
-        <v>92</v>
-      </c>
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H69" s="17">
-        <v>19.1738</v>
-      </c>
-      <c r="I69" s="17">
-        <v>-96.1342</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M69" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>106</v>
+        <v>55</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
+      <c r="A71" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
+      <c r="L71" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="18" t="s">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H72" s="14">
+      <c r="H73" s="19">
+        <v>19.1738</v>
+      </c>
+      <c r="I73" s="19">
+        <v>-96.1342</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="H74" s="19">
+        <v>19.1738</v>
+      </c>
+      <c r="I74" s="19">
+        <v>-96.1342</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H77" s="8">
         <v>-52.33039</v>
       </c>
-      <c r="I72" s="14">
+      <c r="I77" s="8">
         <v>-68.3444</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="M72" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H73" s="19">
-        <v>-52.0667</v>
-      </c>
-      <c r="I73" s="19">
-        <v>-66.7006</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L73" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H74" s="19">
-        <v>-50.8631</v>
-      </c>
-      <c r="I74" s="19">
-        <v>-64.4367</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L74" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H75" s="19">
-        <v>-49.475</v>
-      </c>
-      <c r="I75" s="19">
-        <v>-62.2117</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L75" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="M75" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H76" s="19">
-        <v>-48.7006</v>
-      </c>
-      <c r="I76" s="19">
-        <v>-61.0917</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L76" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3"/>
-      <c r="B77" s="4"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
+      <c r="J77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="E78" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="H78" s="21">
+        <v>-52.0667</v>
+      </c>
+      <c r="I78" s="21">
+        <v>-66.7006</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="H78" s="14">
-        <v>-12.0611</v>
-      </c>
-      <c r="I78" s="14">
-        <v>-77.1469</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L78" s="7" t="s">
+      <c r="M78" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="M78" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3"/>
-      <c r="B79" s="4"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
+      <c r="B79" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H79" s="21">
+        <v>-50.8631</v>
+      </c>
+      <c r="I79" s="21">
+        <v>-64.4367</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3"/>
-      <c r="B80" s="4"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
+      <c r="A80" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H80" s="21">
+        <v>-49.475</v>
+      </c>
+      <c r="I80" s="21">
+        <v>-62.2117</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H81" s="17">
-        <v>19.1738</v>
-      </c>
-      <c r="I81" s="17">
-        <v>-96.1342</v>
+      <c r="A81" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H81" s="21">
+        <v>-48.7006</v>
+      </c>
+      <c r="I81" s="21">
+        <v>-61.0917</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>16</v>
@@ -3070,43 +3186,39 @@
       <c r="K81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L81" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="M81" s="12" t="s">
-        <v>19</v>
+      <c r="L81" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="22"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="4"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" s="15" t="s">
-        <v>124</v>
+      <c r="B83" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>131</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G83" s="4"/>
-      <c r="H83" s="24">
-        <v>-39.0</v>
-      </c>
-      <c r="I83" s="24">
-        <v>-37.6389</v>
+        <v>132</v>
+      </c>
+      <c r="H83" s="8">
+        <v>-12.0611</v>
+      </c>
+      <c r="I83" s="8">
+        <v>-77.1469</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>16</v>
@@ -3115,1045 +3227,1469 @@
         <v>17</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="M83" s="4" t="s">
-        <v>26</v>
+        <v>133</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B84" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G84" s="4"/>
-      <c r="H84" s="24">
-        <v>-18.0</v>
-      </c>
-      <c r="I84" s="24">
-        <v>-27.6389</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L84" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="M84" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A84" s="3"/>
+      <c r="B84" s="4"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B85" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G85" s="4"/>
-      <c r="H85" s="24">
-        <v>15.0</v>
-      </c>
-      <c r="I85" s="24">
-        <v>-32.2222</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L85" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="M85" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A85" s="3"/>
+      <c r="B85" s="4"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="7"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="22"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c r="A86" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="H86" s="19">
+        <v>19.1738</v>
+      </c>
+      <c r="I86" s="19">
+        <v>-96.1342</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L86" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M86" s="15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B87" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>125</v>
-      </c>
+      <c r="A87" s="10"/>
+      <c r="B87" s="7"/>
       <c r="G87" s="4"/>
-      <c r="H87" s="14">
-        <v>36.5298</v>
-      </c>
-      <c r="I87" s="14">
-        <v>-6.2923</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9"/>
       <c r="L87" s="7"/>
-      <c r="M87" s="12" t="s">
-        <v>92</v>
-      </c>
+      <c r="M87" s="7"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B88" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="A88" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G88" s="4"/>
       <c r="H88" s="8">
-        <v>36.4942</v>
-      </c>
-      <c r="I88" s="14">
-        <v>-6.206542</v>
+        <v>37.585</v>
+      </c>
+      <c r="I88" s="8">
+        <v>-0.968</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="L88" s="7"/>
-      <c r="M88" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="M88" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6"/>
+      <c r="A89" s="10"/>
       <c r="B89" s="7"/>
       <c r="G89" s="4"/>
-      <c r="H89" s="14"/>
-      <c r="I89" s="14"/>
-      <c r="J89" s="22"/>
-      <c r="K89" s="22"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G90" s="4" t="s">
+      <c r="A90" s="10"/>
+      <c r="B90" s="7"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="7"/>
+      <c r="M90" s="7"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="H91" s="24">
+        <v>-39.0</v>
+      </c>
+      <c r="I91" s="24">
+        <v>-37.6389</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L91" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="10"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="17"/>
+      <c r="E92" s="7"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="24"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="4"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="H90" s="24">
-        <v>43.4791</v>
-      </c>
-      <c r="I90" s="24">
-        <v>-8.2375</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L90" s="7" t="s">
+      <c r="C93" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="M90" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="7"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="22"/>
-      <c r="K91" s="22"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6" t="s">
+      <c r="E93" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D92" s="26"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="14">
-        <v>43.476</v>
-      </c>
-      <c r="I92" s="14">
-        <v>-8.286</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L92" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="M92" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="7"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
+      <c r="H93" s="8">
+        <v>37.05996</v>
+      </c>
+      <c r="I93" s="8">
+        <v>15.2826</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>136</v>
-      </c>
+      <c r="A94" s="10"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="17"/>
+      <c r="E94" s="7"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="14">
-        <v>43.476</v>
-      </c>
-      <c r="I94" s="14">
-        <v>-8.286</v>
-      </c>
-      <c r="J94" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L94" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="M94" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="7"/>
+      <c r="M94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>136</v>
+      <c r="A95" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B95" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="14">
-        <v>43.476</v>
-      </c>
-      <c r="I95" s="14">
-        <v>-8.286</v>
-      </c>
-      <c r="J95" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K95" s="22" t="s">
+      <c r="H95" s="24">
+        <v>-18.0</v>
+      </c>
+      <c r="I95" s="24">
+        <v>-27.6389</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="M95" s="7" t="s">
-        <v>19</v>
+        <v>133</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>136</v>
-      </c>
+      <c r="A96" s="10"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="17"/>
+      <c r="E96" s="7"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="14">
-        <v>43.476</v>
-      </c>
-      <c r="I96" s="14">
-        <v>-8.286</v>
-      </c>
-      <c r="J96" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K96" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="M96" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="14">
-        <v>43.476</v>
-      </c>
-      <c r="I97" s="14">
-        <v>-8.286</v>
-      </c>
-      <c r="J97" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K97" s="22" t="s">
+      <c r="H97" s="8">
+        <v>39.8125</v>
+      </c>
+      <c r="I97" s="8">
+        <v>25.9889</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="M97" s="7" t="s">
-        <v>19</v>
+        <v>146</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E98" s="7" t="s">
+      <c r="A98" s="10"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="17"/>
+      <c r="E98" s="7"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="4"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="G98" s="4"/>
-      <c r="J98" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K98" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L98" s="7" t="s">
+      <c r="B99" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="I99" s="24">
+        <v>-32.2222</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="10"/>
+      <c r="B100" s="7"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="7"/>
+      <c r="M100" s="7"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="M98" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="6" t="s">
+      <c r="B101" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G101" s="4"/>
+      <c r="H101" s="8">
+        <v>41.0198</v>
+      </c>
+      <c r="I101" s="8">
+        <v>28.9793</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L101" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G99" s="4"/>
-      <c r="J99" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K99" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L99" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="M99" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="6" t="s">
+      <c r="M101" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="7"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="7"/>
+      <c r="M102" s="7"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G100" s="4"/>
-      <c r="J100" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K100" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="M100" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="3"/>
-      <c r="B101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="3"/>
-      <c r="B102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="3"/>
-      <c r="B103" s="4"/>
+      <c r="B103" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>132</v>
+      </c>
       <c r="G103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
+      <c r="H103" s="8">
+        <v>36.5298</v>
+      </c>
+      <c r="I103" s="8">
+        <v>-6.2923</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L103" s="7"/>
+      <c r="M103" s="15" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="10"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="17"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="11"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="7"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G104" s="4"/>
-      <c r="H104" s="27">
-        <v>18.47</v>
-      </c>
-      <c r="I104" s="27">
-        <v>-66.126</v>
-      </c>
-      <c r="J104" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K104" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L104" s="7" t="s">
+      <c r="B105" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M104" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="6" t="s">
+      <c r="G105" s="4"/>
+      <c r="H105" s="11">
+        <v>41.0198</v>
+      </c>
+      <c r="I105" s="8">
+        <v>28.9793</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G105" s="4"/>
-      <c r="H105" s="27">
-        <v>18.47</v>
-      </c>
-      <c r="I105" s="27">
-        <v>-66.126</v>
-      </c>
-      <c r="J105" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K105" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L105" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="M105" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="10"/>
+      <c r="B106" s="23"/>
+      <c r="C106" s="17"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="7"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G106" s="4"/>
-      <c r="H106" s="27">
-        <v>18.47</v>
-      </c>
-      <c r="I106" s="27">
-        <v>-66.126</v>
-      </c>
-      <c r="J106" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K106" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L106" s="7" t="s">
+      <c r="B107" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H107" s="11">
+        <v>36.4942</v>
+      </c>
+      <c r="I107" s="8">
+        <v>-6.206542</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L107" s="7"/>
+      <c r="M107" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="10"/>
+      <c r="B108" s="7"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="7"/>
+      <c r="M108" s="7"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E109" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M106" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G107" s="4"/>
-      <c r="J107" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K107" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L107" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="M107" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="6" t="s">
+      <c r="G109" s="4"/>
+      <c r="H109" s="8">
+        <v>39.8873</v>
+      </c>
+      <c r="I109" s="8">
+        <v>4.285</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L109" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G108" s="4"/>
-      <c r="H108" s="14">
-        <v>23.1597</v>
-      </c>
-      <c r="I108" s="14">
-        <v>-82.3533</v>
-      </c>
-      <c r="J108" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K108" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L108" s="7" t="s">
+      <c r="M109" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="M108" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="3"/>
-      <c r="B109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="6" t="s">
+      <c r="B110" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="8">
+        <v>36.5298</v>
+      </c>
+      <c r="I110" s="8">
+        <v>-6.2923</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110" s="7"/>
+      <c r="M110" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="10"/>
+      <c r="B111" s="7"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="7"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="10"/>
+      <c r="B112" s="7"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="7"/>
+      <c r="M112" s="7"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B110" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G110" s="4"/>
-      <c r="H110" s="14">
-        <v>23.1597</v>
-      </c>
-      <c r="I110" s="14">
-        <v>-82.3533</v>
-      </c>
-      <c r="J110" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K110" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L110" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="M110" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="28"/>
-      <c r="B111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="6" t="s">
+      <c r="B113" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B112" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G112" s="4"/>
-      <c r="H112" s="14">
-        <v>19.1738</v>
-      </c>
-      <c r="I112" s="14">
-        <v>-96.1342</v>
-      </c>
-      <c r="J112" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K112" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L112" s="7" t="s">
+      <c r="C113" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="M112" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="28"/>
-      <c r="B113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
+      <c r="G113" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H113" s="24">
+        <v>43.4791</v>
+      </c>
+      <c r="I113" s="24">
+        <v>-8.2375</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="M113" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>136</v>
-      </c>
+      <c r="A114" s="10"/>
+      <c r="B114" s="7"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="14">
-        <v>23.1597</v>
-      </c>
-      <c r="I114" s="14">
-        <v>-82.3533</v>
-      </c>
-      <c r="J114" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K114" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L114" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="M114" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="28"/>
-      <c r="B115" s="4"/>
+      <c r="A115" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D115" s="26"/>
       <c r="G115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="4"/>
+      <c r="H115" s="8">
+        <v>43.476</v>
+      </c>
+      <c r="I115" s="8">
+        <v>-8.286</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M115" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="28"/>
-      <c r="B116" s="4"/>
+      <c r="A116" s="10"/>
+      <c r="B116" s="7"/>
       <c r="G116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="4"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="7"/>
+      <c r="M116" s="7"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="6" t="s">
-        <v>162</v>
+      <c r="A117" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C117" s="15" t="s">
-        <v>136</v>
+        <v>159</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="G117" s="4"/>
-      <c r="H117" s="27">
-        <v>36.4942</v>
-      </c>
-      <c r="I117" s="27">
-        <v>-6.206542</v>
-      </c>
-      <c r="J117" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K117" s="22" t="s">
+      <c r="H117" s="8">
+        <v>43.476</v>
+      </c>
+      <c r="I117" s="8">
+        <v>-8.286</v>
+      </c>
+      <c r="J117" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="M117" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="6" t="s">
-        <v>163</v>
+      <c r="A118" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>136</v>
+        <v>159</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="G118" s="4"/>
-      <c r="H118" s="27">
-        <v>36.4942</v>
-      </c>
-      <c r="I118" s="27">
-        <v>-6.206542</v>
-      </c>
-      <c r="J118" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K118" s="22" t="s">
+      <c r="H118" s="8">
+        <v>43.476</v>
+      </c>
+      <c r="I118" s="8">
+        <v>-8.286</v>
+      </c>
+      <c r="J118" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K118" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="M118" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="3"/>
-      <c r="B119" s="4"/>
+      <c r="A119" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>160</v>
+      </c>
       <c r="G119" s="4"/>
-      <c r="J119" s="4"/>
-      <c r="K119" s="4"/>
+      <c r="H119" s="8">
+        <v>43.476</v>
+      </c>
+      <c r="I119" s="8">
+        <v>-8.286</v>
+      </c>
+      <c r="J119" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K119" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L119" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M119" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="6" t="s">
-        <v>164</v>
+      <c r="A120" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H120" s="27">
-        <v>36.495516</v>
-      </c>
-      <c r="I120" s="27">
-        <v>-6.18334</v>
-      </c>
-      <c r="J120" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K120" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G120" s="4"/>
+      <c r="H120" s="8">
+        <v>43.476</v>
+      </c>
+      <c r="I120" s="8">
+        <v>-8.286</v>
+      </c>
+      <c r="J120" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K120" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>166</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="28"/>
-      <c r="B121" s="4"/>
+      <c r="A121" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="G121" s="4"/>
-      <c r="J121" s="4"/>
-      <c r="K121" s="4"/>
+      <c r="J121" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L121" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="6" t="s">
-        <v>168</v>
+      <c r="A122" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C122" s="15" t="s">
-        <v>136</v>
+        <v>159</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="G122" s="4"/>
-      <c r="H122" s="27">
-        <v>36.4942</v>
-      </c>
-      <c r="I122" s="27">
-        <v>-6.206542</v>
-      </c>
-      <c r="J122" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K122" s="22" t="s">
+      <c r="J122" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K122" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="M122" s="7" t="s">
-        <v>19</v>
+        <v>172</v>
+      </c>
+      <c r="M122" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="3"/>
-      <c r="B123" s="4"/>
+      <c r="A123" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="G123" s="4"/>
-      <c r="J123" s="4"/>
-      <c r="K123" s="4"/>
+      <c r="J123" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L123" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M123" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H124" s="12">
-        <v>36.4942</v>
-      </c>
-      <c r="I124" s="12">
-        <v>-6.206542</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="K124" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M124" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="3"/>
+      <c r="B125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="3"/>
+      <c r="B126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+    </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="9" t="s">
-        <v>170</v>
+      <c r="A127" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="B127" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E127" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C127" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H127" s="14">
-        <v>36.5298</v>
-      </c>
-      <c r="I127" s="14">
-        <v>-6.2923</v>
-      </c>
-      <c r="J127" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K127" s="22" t="s">
+      <c r="G127" s="4"/>
+      <c r="H127" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I127" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J127" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K127" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="M127" s="4" t="s">
-        <v>26</v>
+        <v>176</v>
+      </c>
+      <c r="M127" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="9" t="s">
-        <v>175</v>
+      <c r="A128" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="B128" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E128" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C128" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>173</v>
-      </c>
+      <c r="G128" s="4"/>
       <c r="H128" s="27">
         <v>18.47</v>
       </c>
       <c r="I128" s="27">
         <v>-66.126</v>
       </c>
-      <c r="J128" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K128" s="22" t="s">
+      <c r="J128" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K128" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L128" s="7" t="s">
         <v>176</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="9" t="s">
-        <v>177</v>
+      <c r="A129" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="B129" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E129" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="G129" s="4"/>
+      <c r="H129" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I129" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J129" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="M129" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G130" s="4"/>
+      <c r="J130" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L130" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="E129" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H129" s="14">
+      <c r="M130" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G131" s="4"/>
+      <c r="H131" s="8">
         <v>23.1597</v>
       </c>
-      <c r="I129" s="14">
+      <c r="I131" s="8">
         <v>-82.3533</v>
       </c>
-      <c r="J129" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K129" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="M129" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
+      <c r="J131" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L131" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="M131" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="3"/>
+      <c r="B132" s="4"/>
+      <c r="G132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="4"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G133" s="4"/>
+      <c r="H133" s="8">
+        <v>23.1597</v>
+      </c>
+      <c r="I133" s="8">
+        <v>-82.3533</v>
+      </c>
+      <c r="J133" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L133" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M133" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="28"/>
+      <c r="B134" s="4"/>
+      <c r="G134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C135" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G135" s="4"/>
+      <c r="H135" s="8">
+        <v>19.1738</v>
+      </c>
+      <c r="I135" s="8">
+        <v>-96.1342</v>
+      </c>
+      <c r="J135" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="M135" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="28"/>
+      <c r="B136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G137" s="4"/>
+      <c r="H137" s="8">
+        <v>23.1597</v>
+      </c>
+      <c r="I137" s="8">
+        <v>-82.3533</v>
+      </c>
+      <c r="J137" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L137" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M137" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="28"/>
+      <c r="B138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="28"/>
+      <c r="B139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G140" s="4"/>
+      <c r="H140" s="27">
+        <v>36.4942</v>
+      </c>
+      <c r="I140" s="27">
+        <v>-6.206542</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M140" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G141" s="4"/>
+      <c r="H141" s="27">
+        <v>36.4942</v>
+      </c>
+      <c r="I141" s="27">
+        <v>-6.206542</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L141" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M141" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="3"/>
+      <c r="B142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H143" s="27">
+        <v>36.495516</v>
+      </c>
+      <c r="I143" s="27">
+        <v>-6.18334</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L143" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="M143" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="28"/>
+      <c r="B144" s="4"/>
+      <c r="G144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G145" s="4"/>
+      <c r="H145" s="27">
+        <v>36.4942</v>
+      </c>
+      <c r="I145" s="27">
+        <v>-6.206542</v>
+      </c>
+      <c r="J145" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L145" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M145" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="3"/>
+      <c r="B146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H147" s="15">
+        <v>36.4942</v>
+      </c>
+      <c r="I147" s="15">
+        <v>-6.206542</v>
+      </c>
+      <c r="J147" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M147" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="148" ht="15.75" customHeight="1"/>
     <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H150" s="8">
+        <v>36.5298</v>
+      </c>
+      <c r="I150" s="8">
+        <v>-6.2923</v>
+      </c>
+      <c r="J150" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L150" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="M150" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H151" s="27">
+        <v>18.47</v>
+      </c>
+      <c r="I151" s="27">
+        <v>-66.126</v>
+      </c>
+      <c r="J151" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L151" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M151" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H152" s="8">
+        <v>23.1597</v>
+      </c>
+      <c r="I152" s="8">
+        <v>-82.3533</v>
+      </c>
+      <c r="J152" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L152" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="M152" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="153" ht="15.75" customHeight="1"/>
     <row r="154" ht="15.75" customHeight="1"/>
     <row r="155" ht="15.75" customHeight="1"/>
@@ -5056,6 +5592,29 @@
     <row r="1052" ht="15.75" customHeight="1"/>
     <row r="1053" ht="15.75" customHeight="1"/>
     <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
+    <row r="1071" ht="15.75" customHeight="1"/>
+    <row r="1072" ht="15.75" customHeight="1"/>
+    <row r="1073" ht="15.75" customHeight="1"/>
+    <row r="1074" ht="15.75" customHeight="1"/>
+    <row r="1075" ht="15.75" customHeight="1"/>
+    <row r="1076" ht="15.75" customHeight="1"/>
+    <row r="1077" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/lat_claude.xlsx
+++ b/lat_claude.xlsx
@@ -738,6 +738,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -775,9 +778,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -1115,11 +1115,11 @@
         <v>21</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="8">
-        <v>37.1718</v>
-      </c>
-      <c r="I4" s="8">
-        <v>4.5003</v>
+      <c r="H4" s="10">
+        <v>36.1718</v>
+      </c>
+      <c r="I4" s="10">
+        <v>-4.5003</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>16</v>
@@ -2473,7 +2473,7 @@
       <c r="M51" s="4"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="11" t="s">
         <v>85</v>
       </c>
       <c r="B52" s="7"/>
@@ -2486,10 +2486,10 @@
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="11">
+      <c r="H52" s="12">
         <v>-12.0611</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="12">
         <v>-77.1469</v>
       </c>
       <c r="J52" s="4" t="s">
@@ -2506,7 +2506,7 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B53" s="7"/>
@@ -2519,10 +2519,10 @@
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="13">
+      <c r="H53" s="14">
         <v>-42.61667</v>
       </c>
-      <c r="I53" s="13">
+      <c r="I53" s="14">
         <v>-76.1923</v>
       </c>
       <c r="J53" s="4"/>
@@ -2535,13 +2535,13 @@
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D54" s="7"/>
@@ -2550,10 +2550,10 @@
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="13">
+      <c r="H54" s="14">
         <v>-42.61667</v>
       </c>
-      <c r="I54" s="13">
+      <c r="I54" s="14">
         <v>-76.1923</v>
       </c>
       <c r="J54" s="4" t="s">
@@ -2570,22 +2570,22 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="11" t="s">
         <v>94</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D55" s="7"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="11">
+      <c r="H55" s="12">
         <v>-36.7382</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="12">
         <v>-73.1388</v>
       </c>
       <c r="J55" s="4" t="s">
@@ -2597,12 +2597,12 @@
       <c r="L55" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="M55" s="15" t="s">
+      <c r="M55" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="11" t="s">
         <v>96</v>
       </c>
       <c r="B56" s="7"/>
@@ -2615,10 +2615,10 @@
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="11">
+      <c r="H56" s="12">
         <v>-22.881353</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="12">
         <v>-43.182717</v>
       </c>
       <c r="J56" s="4" t="s">
@@ -2627,33 +2627,33 @@
       <c r="K56" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M56" s="15" t="s">
+      <c r="M56" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="16"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="13" t="s">
         <v>97</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D58" s="7"/>
@@ -2662,10 +2662,10 @@
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="11">
+      <c r="H58" s="12">
         <v>-36.7382</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="12">
         <v>-73.1388</v>
       </c>
       <c r="J58" s="4" t="s">
@@ -2682,22 +2682,22 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="15" t="s">
         <v>91</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="12">
         <v>-12.0611</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="12">
         <v>-77.1469</v>
       </c>
       <c r="J59" s="4" t="s">
@@ -2706,7 +2706,7 @@
       <c r="K59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M59" s="15" t="s">
+      <c r="M59" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       <c r="M62" s="4"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="11" t="s">
         <v>100</v>
       </c>
       <c r="B63" s="7"/>
@@ -2751,27 +2751,27 @@
       <c r="K63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="15" t="s">
+      <c r="M63" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="11" t="s">
         <v>101</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="18" t="s">
         <v>103</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="11">
+      <c r="H64" s="12">
         <v>36.4942</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="12">
         <v>-6.206542</v>
       </c>
       <c r="J64" s="4" t="s">
@@ -2788,13 +2788,13 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="11" t="s">
         <v>105</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="19" t="s">
         <v>103</v>
       </c>
       <c r="D65" s="4"/>
@@ -2803,10 +2803,10 @@
       <c r="G65" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="12">
         <v>36.4942</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="12">
         <v>-6.206542</v>
       </c>
       <c r="J65" s="4" t="s">
@@ -2815,7 +2815,7 @@
       <c r="K65" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M65" s="15" t="s">
+      <c r="M65" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2834,13 +2834,13 @@
       <c r="M66" s="4"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="18" t="s">
         <v>111</v>
       </c>
       <c r="E67" s="4"/>
@@ -2848,10 +2848,10 @@
       <c r="G67" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="12">
         <v>36.4942</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="12">
         <v>-6.206542</v>
       </c>
       <c r="J67" s="4" t="s">
@@ -2860,7 +2860,7 @@
       <c r="K67" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M67" s="15" t="s">
+      <c r="M67" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       <c r="B70" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="19" t="s">
         <v>113</v>
       </c>
       <c r="D70" s="4"/>
@@ -2925,7 +2925,7 @@
       <c r="B71" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="19" t="s">
         <v>113</v>
       </c>
       <c r="D71" s="4"/>
@@ -2969,13 +2969,13 @@
       <c r="B73" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="H73" s="19">
+      <c r="H73" s="20">
         <v>19.1738</v>
       </c>
-      <c r="I73" s="19">
+      <c r="I73" s="20">
         <v>-96.1342</v>
       </c>
       <c r="J73" s="4" t="s">
@@ -2984,7 +2984,7 @@
       <c r="K73" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="15" t="s">
+      <c r="M73" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2995,13 +2995,13 @@
       <c r="B74" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="H74" s="19">
+      <c r="H74" s="20">
         <v>19.1738</v>
       </c>
-      <c r="I74" s="19">
+      <c r="I74" s="20">
         <v>-96.1342</v>
       </c>
       <c r="J74" s="4" t="s">
@@ -3010,7 +3010,7 @@
       <c r="K74" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M74" s="15" t="s">
+      <c r="M74" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       <c r="B75" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="18" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       <c r="K76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="21" t="s">
         <v>120</v>
       </c>
       <c r="B77" s="7" t="s">
@@ -3066,7 +3066,7 @@
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="21" t="s">
         <v>125</v>
       </c>
       <c r="B78" s="7" t="s">
@@ -3078,10 +3078,10 @@
       <c r="E78" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H78" s="21">
+      <c r="H78" s="22">
         <v>-52.0667</v>
       </c>
-      <c r="I78" s="21">
+      <c r="I78" s="22">
         <v>-66.7006</v>
       </c>
       <c r="J78" s="4" t="s">
@@ -3098,7 +3098,7 @@
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="20" t="s">
+      <c r="A79" s="21" t="s">
         <v>126</v>
       </c>
       <c r="B79" s="7" t="s">
@@ -3110,10 +3110,10 @@
       <c r="E79" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H79" s="21">
+      <c r="H79" s="22">
         <v>-50.8631</v>
       </c>
-      <c r="I79" s="21">
+      <c r="I79" s="22">
         <v>-64.4367</v>
       </c>
       <c r="J79" s="4" t="s">
@@ -3130,7 +3130,7 @@
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="11" t="s">
         <v>127</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -3142,10 +3142,10 @@
       <c r="E80" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H80" s="21">
+      <c r="H80" s="22">
         <v>-49.475</v>
       </c>
-      <c r="I80" s="21">
+      <c r="I80" s="22">
         <v>-62.2117</v>
       </c>
       <c r="J80" s="4" t="s">
@@ -3162,7 +3162,7 @@
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="11" t="s">
         <v>128</v>
       </c>
       <c r="B81" s="7" t="s">
@@ -3174,10 +3174,10 @@
       <c r="E81" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H81" s="21">
+      <c r="H81" s="22">
         <v>-48.7006</v>
       </c>
-      <c r="I81" s="21">
+      <c r="I81" s="22">
         <v>-61.0917</v>
       </c>
       <c r="J81" s="4" t="s">
@@ -3196,8 +3196,8 @@
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="4"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
     </row>
@@ -3205,10 +3205,10 @@
       <c r="A83" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="18" t="s">
         <v>131</v>
       </c>
       <c r="E83" s="7" t="s">
@@ -3236,16 +3236,16 @@
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="4"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="19"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
     </row>
@@ -3256,13 +3256,13 @@
       <c r="B86" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="H86" s="19">
+      <c r="H86" s="20">
         <v>19.1738</v>
       </c>
-      <c r="I86" s="19">
+      <c r="I86" s="20">
         <v>-96.1342</v>
       </c>
       <c r="J86" s="4" t="s">
@@ -3271,15 +3271,15 @@
       <c r="K86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L86" s="15" t="s">
+      <c r="L86" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="M86" s="15" t="s">
+      <c r="M86" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="10"/>
+      <c r="A87" s="11"/>
       <c r="B87" s="7"/>
       <c r="G87" s="4"/>
       <c r="H87" s="8"/>
@@ -3290,7 +3290,7 @@
       <c r="M87" s="7"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="11" t="s">
         <v>136</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -3323,7 +3323,7 @@
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="10"/>
+      <c r="A89" s="11"/>
       <c r="B89" s="7"/>
       <c r="G89" s="4"/>
       <c r="H89" s="8"/>
@@ -3334,7 +3334,7 @@
       <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="10"/>
+      <c r="A90" s="11"/>
       <c r="B90" s="7"/>
       <c r="G90" s="4"/>
       <c r="H90" s="8"/>
@@ -3345,23 +3345,23 @@
       <c r="M90" s="7"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="18" t="s">
         <v>131</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>132</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="24">
+      <c r="H91" s="10">
         <v>-39.0</v>
       </c>
-      <c r="I91" s="24">
+      <c r="I91" s="10">
         <v>-37.6389</v>
       </c>
       <c r="J91" s="4" t="s">
@@ -3378,20 +3378,20 @@
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="10"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="17"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="18"/>
       <c r="E92" s="7"/>
       <c r="G92" s="4"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="24"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="7"/>
       <c r="M92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="11" t="s">
         <v>142</v>
       </c>
       <c r="B93" s="7" t="s">
@@ -3424,36 +3424,36 @@
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="17"/>
+      <c r="A94" s="11"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="18"/>
       <c r="E94" s="7"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="24"/>
+      <c r="H94" s="10"/>
+      <c r="I94" s="10"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="7"/>
       <c r="M94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="18" t="s">
         <v>131</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>132</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="24">
+      <c r="H95" s="10">
         <v>-18.0</v>
       </c>
-      <c r="I95" s="24">
+      <c r="I95" s="10">
         <v>-27.6389</v>
       </c>
       <c r="J95" s="4" t="s">
@@ -3470,20 +3470,20 @@
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="10"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="17"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="18"/>
       <c r="E96" s="7"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="24"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="7"/>
       <c r="M96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="11" t="s">
         <v>145</v>
       </c>
       <c r="B97" s="7" t="s">
@@ -3516,36 +3516,36 @@
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-      <c r="B98" s="23"/>
-      <c r="C98" s="17"/>
+      <c r="A98" s="11"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="18"/>
       <c r="E98" s="7"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
+      <c r="H98" s="10"/>
+      <c r="I98" s="10"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="7"/>
       <c r="M98" s="4"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B99" s="23" t="s">
+      <c r="B99" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="18" t="s">
         <v>131</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>132</v>
       </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="24">
+      <c r="H99" s="10">
         <v>15.0</v>
       </c>
-      <c r="I99" s="24">
+      <c r="I99" s="10">
         <v>-32.2222</v>
       </c>
       <c r="J99" s="4" t="s">
@@ -3562,7 +3562,7 @@
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
+      <c r="A100" s="11"/>
       <c r="B100" s="7"/>
       <c r="G100" s="4"/>
       <c r="H100" s="8"/>
@@ -3573,7 +3573,7 @@
       <c r="M100" s="7"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="11" t="s">
         <v>148</v>
       </c>
       <c r="B101" s="7" t="s">
@@ -3601,12 +3601,12 @@
       <c r="L101" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="M101" s="15" t="s">
+      <c r="M101" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
+      <c r="A102" s="11"/>
       <c r="B102" s="7"/>
       <c r="G102" s="4"/>
       <c r="H102" s="8"/>
@@ -3617,13 +3617,13 @@
       <c r="M102" s="7"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B103" s="23" t="s">
+      <c r="B103" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="18" t="s">
         <v>131</v>
       </c>
       <c r="E103" s="7" t="s">
@@ -3643,23 +3643,23 @@
         <v>17</v>
       </c>
       <c r="L103" s="7"/>
-      <c r="M103" s="15" t="s">
+      <c r="M103" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="23"/>
-      <c r="C104" s="17"/>
+      <c r="A104" s="11"/>
+      <c r="B104" s="24"/>
+      <c r="C104" s="18"/>
       <c r="G104" s="4"/>
-      <c r="H104" s="11"/>
+      <c r="H104" s="12"/>
       <c r="I104" s="8"/>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="7"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="11" t="s">
         <v>151</v>
       </c>
       <c r="B105" s="7" t="s">
@@ -3672,7 +3672,7 @@
         <v>152</v>
       </c>
       <c r="G105" s="4"/>
-      <c r="H105" s="11">
+      <c r="H105" s="12">
         <v>41.0198</v>
       </c>
       <c r="I105" s="8">
@@ -3692,30 +3692,30 @@
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="B106" s="23"/>
-      <c r="C106" s="17"/>
+      <c r="A106" s="11"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="18"/>
       <c r="G106" s="4"/>
-      <c r="H106" s="11"/>
+      <c r="H106" s="12"/>
       <c r="I106" s="8"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="7"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B107" s="23" t="s">
+      <c r="B107" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C107" s="17" t="s">
+      <c r="C107" s="18" t="s">
         <v>131</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="12">
         <v>36.4942</v>
       </c>
       <c r="I107" s="8">
@@ -3728,12 +3728,12 @@
         <v>108</v>
       </c>
       <c r="L107" s="7"/>
-      <c r="M107" s="15" t="s">
+      <c r="M107" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="10"/>
+      <c r="A108" s="11"/>
       <c r="B108" s="7"/>
       <c r="G108" s="4"/>
       <c r="H108" s="8"/>
@@ -3744,7 +3744,7 @@
       <c r="M108" s="7"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="11" t="s">
         <v>155</v>
       </c>
       <c r="B109" s="7" t="s">
@@ -3772,12 +3772,12 @@
       <c r="L109" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M109" s="15" t="s">
+      <c r="M109" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="11" t="s">
         <v>157</v>
       </c>
       <c r="B110" s="7" t="s">
@@ -3808,7 +3808,7 @@
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="10"/>
+      <c r="A111" s="11"/>
       <c r="B111" s="7"/>
       <c r="G111" s="4"/>
       <c r="H111" s="8"/>
@@ -3819,7 +3819,7 @@
       <c r="M111" s="7"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="10"/>
+      <c r="A112" s="11"/>
       <c r="B112" s="7"/>
       <c r="G112" s="4"/>
       <c r="H112" s="8"/>
@@ -3830,22 +3830,22 @@
       <c r="M112" s="7"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="11" t="s">
         <v>158</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H113" s="24">
+      <c r="H113" s="10">
         <v>43.4791</v>
       </c>
-      <c r="I113" s="24">
+      <c r="I113" s="10">
         <v>-8.2375</v>
       </c>
       <c r="J113" s="4" t="s">
@@ -3862,7 +3862,7 @@
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="10"/>
+      <c r="A114" s="11"/>
       <c r="B114" s="7"/>
       <c r="G114" s="4"/>
       <c r="H114" s="8"/>
@@ -3873,7 +3873,7 @@
       <c r="M114" s="7"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B115" s="7" t="s">
@@ -3904,7 +3904,7 @@
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="10"/>
+      <c r="A116" s="11"/>
       <c r="B116" s="7"/>
       <c r="G116" s="4"/>
       <c r="H116" s="8"/>
@@ -3915,13 +3915,13 @@
       <c r="M116" s="7"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="C117" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G117" s="4"/>
@@ -3945,13 +3945,13 @@
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="C118" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G118" s="4"/>
@@ -3975,13 +3975,13 @@
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G119" s="4"/>
@@ -4005,13 +4005,13 @@
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="10" t="s">
+      <c r="A120" s="11" t="s">
         <v>169</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C120" s="17" t="s">
+      <c r="C120" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G120" s="4"/>
@@ -4035,13 +4035,13 @@
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="11" t="s">
         <v>170</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E121" s="7" t="s">
@@ -4062,13 +4062,13 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="11" t="s">
         <v>173</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E122" s="7" t="s">
@@ -4089,13 +4089,13 @@
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="11" t="s">
         <v>174</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E123" s="7" t="s">
@@ -4137,13 +4137,13 @@
       <c r="K126" s="4"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="11" t="s">
         <v>175</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E127" s="7" t="s">
@@ -4170,13 +4170,13 @@
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="11" t="s">
         <v>177</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C128" s="17" t="s">
+      <c r="C128" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E128" s="7" t="s">
@@ -4203,13 +4203,13 @@
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="10" t="s">
+      <c r="A129" s="11" t="s">
         <v>178</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C129" s="17" t="s">
+      <c r="C129" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E129" s="7" t="s">
@@ -4236,13 +4236,13 @@
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="11" t="s">
         <v>179</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C130" s="17" t="s">
+      <c r="C130" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E130" s="7" t="s">
@@ -4263,13 +4263,13 @@
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="11" t="s">
         <v>180</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="C131" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E131" s="7" t="s">
@@ -4303,13 +4303,13 @@
       <c r="K132" s="4"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="10" t="s">
+      <c r="A133" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C133" s="17" t="s">
+      <c r="C133" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G133" s="4"/>
@@ -4325,7 +4325,7 @@
       <c r="K133" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L133" s="15" t="s">
+      <c r="L133" s="16" t="s">
         <v>135</v>
       </c>
       <c r="M133" s="7" t="s">
@@ -4340,13 +4340,13 @@
       <c r="K134" s="4"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="10" t="s">
+      <c r="A135" s="11" t="s">
         <v>183</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C135" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G135" s="4"/>
@@ -4377,13 +4377,13 @@
       <c r="K136" s="4"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="10" t="s">
+      <c r="A137" s="11" t="s">
         <v>185</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C137" s="17" t="s">
+      <c r="C137" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G137" s="4"/>
@@ -4399,7 +4399,7 @@
       <c r="K137" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L137" s="15" t="s">
+      <c r="L137" s="16" t="s">
         <v>135</v>
       </c>
       <c r="M137" s="7" t="s">
@@ -4421,13 +4421,13 @@
       <c r="K139" s="4"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="10" t="s">
+      <c r="A140" s="11" t="s">
         <v>186</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C140" s="17" t="s">
+      <c r="C140" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G140" s="4"/>
@@ -4451,13 +4451,13 @@
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="10" t="s">
+      <c r="A141" s="11" t="s">
         <v>187</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C141" s="17" t="s">
+      <c r="C141" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G141" s="4"/>
@@ -4488,13 +4488,13 @@
       <c r="K142" s="4"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="10" t="s">
+      <c r="A143" s="11" t="s">
         <v>188</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C143" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G143" s="4" t="s">
@@ -4527,13 +4527,13 @@
       <c r="K144" s="4"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="10" t="s">
+      <c r="A145" s="11" t="s">
         <v>192</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C145" s="18" t="s">
         <v>160</v>
       </c>
       <c r="G145" s="4"/>
@@ -4570,16 +4570,16 @@
       <c r="B147" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C147" s="17" t="s">
+      <c r="C147" s="18" t="s">
         <v>113</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H147" s="15">
+      <c r="H147" s="16">
         <v>36.4942</v>
       </c>
-      <c r="I147" s="15">
+      <c r="I147" s="16">
         <v>-6.206542</v>
       </c>
       <c r="J147" s="4" t="s">
@@ -4588,20 +4588,20 @@
       <c r="K147" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M147" s="15" t="s">
+      <c r="M147" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1"/>
     <row r="149" ht="15.75" customHeight="1"/>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="12" t="s">
+      <c r="A150" s="13" t="s">
         <v>194</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C150" s="17" t="s">
+      <c r="C150" s="18" t="s">
         <v>196</v>
       </c>
       <c r="E150" s="7" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="12" t="s">
+      <c r="A151" s="13" t="s">
         <v>199</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C151" s="17" t="s">
+      <c r="C151" s="18" t="s">
         <v>196</v>
       </c>
       <c r="E151" s="7" t="s">
@@ -4659,13 +4659,13 @@
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="12" t="s">
+      <c r="A152" s="13" t="s">
         <v>201</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C152" s="17" t="s">
+      <c r="C152" s="18" t="s">
         <v>196</v>
       </c>
       <c r="E152" s="7" t="s">
